--- a/DERT_Scouting_REBUILTEventData.xlsx
+++ b/DERT_Scouting_REBUILTEventData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JD Projects\DERT\QRCodeTest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCD1D30F-EBEA-4BDC-A5C3-B48B72361EC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA7099E1-9856-4265-8C93-C55FB5CDF154}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{8F75DEC0-E709-4C38-BCC9-F3572A629777}"/>
+    <workbookView xWindow="3040" yWindow="3040" windowWidth="19200" windowHeight="11170" xr2:uid="{DE87336B-C282-43C1-83B4-ECA0AE3772B8}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1353" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1897" uniqueCount="444">
   <si>
     <t>DERT #2040 - TBA Schedule   (v1.3)</t>
   </si>
@@ -1369,6 +1369,36 @@
   </si>
   <si>
     <t>10/24/2026, 11:00 AM</t>
+  </si>
+  <si>
+    <t>10/24/2026, 11:08 AM</t>
+  </si>
+  <si>
+    <t>10/24/2026, 11:16 AM</t>
+  </si>
+  <si>
+    <t>10/24/2026, 11:32 AM</t>
+  </si>
+  <si>
+    <t>10/24/2026, 11:40 AM</t>
+  </si>
+  <si>
+    <t>10/24/2026, 11:48 AM</t>
+  </si>
+  <si>
+    <t>10/24/2026, 11:56 AM</t>
+  </si>
+  <si>
+    <t>10/24/2026, 12:04 PM</t>
+  </si>
+  <si>
+    <t>10/24/2026, 12:12 PM</t>
+  </si>
+  <si>
+    <t>10/24/2026, 12:20 PM</t>
+  </si>
+  <si>
+    <t>10/24/2026, 12:28 PM</t>
   </si>
 </sst>
 </file>
@@ -1649,49 +1679,49 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{525BCAB4-4AA1-4660-9CD8-3199AB5C6191}" name="Scans" displayName="Scans" ref="A1:AN97" totalsRowShown="0" headerRowDxfId="7">
-  <autoFilter ref="A1:AN97" xr:uid="{525BCAB4-4AA1-4660-9CD8-3199AB5C6191}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A1D2DBDA-7F2A-4BF5-83BD-BA2BFE188EC5}" name="Scans" displayName="Scans" ref="A1:AN157" totalsRowShown="0" headerRowDxfId="7">
+  <autoFilter ref="A1:AN157" xr:uid="{A1D2DBDA-7F2A-4BF5-83BD-BA2BFE188EC5}"/>
   <tableColumns count="40">
-    <tableColumn id="1" xr3:uid="{CB95ADC5-79AF-4052-BA5E-2EEFEE79F7D3}" name="Schema"/>
-    <tableColumn id="2" xr3:uid="{3B38DADE-16A7-4958-9CB1-92649D1424CC}" name="Match type"/>
-    <tableColumn id="3" xr3:uid="{4B544AB0-57B7-4EF1-8875-91AC60D02C68}" name="Match #"/>
-    <tableColumn id="4" xr3:uid="{07CCFC01-2213-4E5E-BA61-109DA01A6DDF}" name="Team #"/>
-    <tableColumn id="5" xr3:uid="{1F94E8A4-FE0A-468A-8B83-CC124CF6F76C}" name="Alliance"/>
-    <tableColumn id="6" xr3:uid="{3E85B78F-583B-4EFB-86D2-0F8117C3A0EB}" name="Station"/>
-    <tableColumn id="7" xr3:uid="{ED701209-417B-4F03-B19A-C0561DD28403}" name="Scout name"/>
-    <tableColumn id="8" xr3:uid="{615E0281-6497-42C1-8420-8B6CEFE288FA}" name="Robot on field?"/>
-    <tableColumn id="9" xr3:uid="{5A684580-BD91-475F-9472-9E614E094A02}" name="Starting position"/>
-    <tableColumn id="10" xr3:uid="{7A30C32B-4541-48C0-8CC7-44372941394B}" name="Fuel preloaded"/>
-    <tableColumn id="11" xr3:uid="{3A56B433-D418-45F8-82B3-28B99999C309}" name="Auto fuel scored"/>
-    <tableColumn id="12" xr3:uid="{98DEED6A-4713-4E3B-811A-5C8855EDE8FA}" name="Auto fuel missed"/>
-    <tableColumn id="13" xr3:uid="{041FD095-073C-4C1E-914C-2D12D06D8B48}" name="Auto path"/>
-    <tableColumn id="14" xr3:uid="{5289C9E7-BF9D-4CFD-9593-0E75A3513DE3}" name="Picked up fuel from"/>
-    <tableColumn id="15" xr3:uid="{C408C99C-09F8-40B8-99CA-0A7A76F96EFA}" name="Tower climb in auto"/>
-    <tableColumn id="16" xr3:uid="{161EAF81-177A-463C-BD63-E268B8EF7F06}" name="Teleop fuel scored"/>
-    <tableColumn id="17" xr3:uid="{96723627-4015-4C80-B5BF-62C50176B6EC}" name="Teleop fuel missed"/>
-    <tableColumn id="18" xr3:uid="{727B2943-0575-4072-BF4C-A734E4FCE9EA}" name="Intake from"/>
-    <tableColumn id="19" xr3:uid="{544E9EFB-EC13-4EBA-88F5-70DE864836C4}" name="Shoots from"/>
-    <tableColumn id="20" xr3:uid="{BF24A142-EBFA-4F1B-8D93-B8D34C97A943}" name="Drives over / through"/>
-    <tableColumn id="21" xr3:uid="{966653A9-4CCA-4676-92F7-0F8EC7C10E68}" name="Inactive Hub behavior"/>
-    <tableColumn id="22" xr3:uid="{30B3B446-B300-4144-8D1C-DAD82B8CC35C}" name="Fuel it can carry"/>
-    <tableColumn id="23" xr3:uid="{2AA1BD3F-FEF7-49CD-ACF3-1A8374906210}" name="Played defense"/>
-    <tableColumn id="24" xr3:uid="{A18FE1DD-C0F3-4BB5-A86D-A6112E79CCA2}" name="Was defended"/>
-    <tableColumn id="25" xr3:uid="{ADCA039D-938C-4B46-A61A-756B48E3A0D0}" name="Tower climb"/>
-    <tableColumn id="26" xr3:uid="{5D6F2BB2-080A-4FC4-B838-CC1996FB2C23}" name="Climb time"/>
-    <tableColumn id="27" xr3:uid="{ACEC8B9C-4353-4303-8604-E7288012DDD2}" name="Driver skill"/>
-    <tableColumn id="28" xr3:uid="{EA44A461-5955-478E-988D-7ABC66872E52}" name="Robot speed"/>
-    <tableColumn id="29" xr3:uid="{984E4961-0FEA-4DF5-8EEC-0EBB9B4945BD}" name="Shooting accuracy"/>
-    <tableColumn id="30" xr3:uid="{FE6F4E7A-F18E-47F5-B6A4-D6B79059DF0B}" name="Problems"/>
-    <tableColumn id="31" xr3:uid="{5D366B49-BC65-4674-B669-9AC80BBA69BE}" name="Minor fouls"/>
-    <tableColumn id="32" xr3:uid="{E39ED6B9-F215-4233-86DD-9A62257A1442}" name="Major fouls"/>
-    <tableColumn id="33" xr3:uid="{7DD8FE47-AABA-4907-8EFB-FF599195AFEF}" name="Card"/>
-    <tableColumn id="34" xr3:uid="{18BD39F6-7585-4814-B767-F41DA7831778}" name="Pick?"/>
-    <tableColumn id="35" xr3:uid="{97A2F8BA-89D6-406F-ACCE-E2DA4596F965}" name="Observations"/>
-    <tableColumn id="36" xr3:uid="{49278A50-3727-47D2-B267-3F3549987FCD}" name="Auto pts" dataDxfId="6"/>
-    <tableColumn id="37" xr3:uid="{1A09AA34-1BE2-4881-9DAA-0E22ABFF5723}" name="Teleop fuel pts" dataDxfId="5"/>
-    <tableColumn id="38" xr3:uid="{574D518F-F93C-47CB-B1AF-91FB22CBA1E1}" name="Climb pts" dataDxfId="4"/>
-    <tableColumn id="39" xr3:uid="{1F9C6587-ABF8-4992-8C34-120DB3D8FF52}" name="Total pts" dataDxfId="3"/>
-    <tableColumn id="40" xr3:uid="{3D3BAFD0-D920-48A1-8C7C-08C354A2A5F7}" name="Submitted"/>
+    <tableColumn id="1" xr3:uid="{4306B822-B157-4C6B-A42B-056E9D3DE5B3}" name="Schema"/>
+    <tableColumn id="2" xr3:uid="{C3BC6BC8-280A-4F7F-8176-BCA308008CE0}" name="Match type"/>
+    <tableColumn id="3" xr3:uid="{91E2FB75-5C4B-4D01-8645-1CF9F10402DB}" name="Match #"/>
+    <tableColumn id="4" xr3:uid="{CC7152AA-60DB-427B-B6F4-7C2584B7C6BB}" name="Team #"/>
+    <tableColumn id="5" xr3:uid="{07A659FF-86B7-4E24-AB13-12C73A05E556}" name="Alliance"/>
+    <tableColumn id="6" xr3:uid="{79F838D3-40B7-4F25-B9F8-F5A7434489C6}" name="Station"/>
+    <tableColumn id="7" xr3:uid="{AAE94F3A-FAC4-497F-A063-1587E2339DC7}" name="Scout name"/>
+    <tableColumn id="8" xr3:uid="{88171AC4-7FEF-4E88-A960-3DA3C57B7333}" name="Robot on field?"/>
+    <tableColumn id="9" xr3:uid="{FD0F7B91-6F4E-451F-A379-5CD7C000A9B7}" name="Starting position"/>
+    <tableColumn id="10" xr3:uid="{15F81305-93FD-455A-B3AE-841BEF4E9614}" name="Fuel preloaded"/>
+    <tableColumn id="11" xr3:uid="{A52D2E95-3B65-4E44-A17D-97AEEA8053B9}" name="Auto fuel scored"/>
+    <tableColumn id="12" xr3:uid="{A2EF3E90-BA7F-4481-B84D-09C3A62CD805}" name="Auto fuel missed"/>
+    <tableColumn id="13" xr3:uid="{E56275BD-4CA2-4C98-B775-1E7EA6B79477}" name="Auto path"/>
+    <tableColumn id="14" xr3:uid="{29248264-4AA7-4F83-9F3F-84E57C653757}" name="Picked up fuel from"/>
+    <tableColumn id="15" xr3:uid="{045674EC-6A29-41B6-898B-1671B6744910}" name="Tower climb in auto"/>
+    <tableColumn id="16" xr3:uid="{C80A5DE4-A9F3-4E86-9541-82C203D045FA}" name="Teleop fuel scored"/>
+    <tableColumn id="17" xr3:uid="{A9581DB8-F743-4DD0-BDA3-502A5CB3F512}" name="Teleop fuel missed"/>
+    <tableColumn id="18" xr3:uid="{570A04C9-7219-45EE-BDAB-C48F6F50AE0F}" name="Intake from"/>
+    <tableColumn id="19" xr3:uid="{B2996772-2330-4481-8847-1A4AB2870804}" name="Shoots from"/>
+    <tableColumn id="20" xr3:uid="{E7D8ED5E-AD1F-4BB1-855A-AE118E927976}" name="Drives over / through"/>
+    <tableColumn id="21" xr3:uid="{FB012918-A02C-49FA-AC94-2A4F2496676D}" name="Inactive Hub behavior"/>
+    <tableColumn id="22" xr3:uid="{0F3B6D6F-E4A0-42B2-ADF2-75791638FBFE}" name="Fuel it can carry"/>
+    <tableColumn id="23" xr3:uid="{8F4F24CB-A3DD-4997-906C-BBC085D214E6}" name="Played defense"/>
+    <tableColumn id="24" xr3:uid="{4581613F-3267-4CC1-9985-54B69D8074CC}" name="Was defended"/>
+    <tableColumn id="25" xr3:uid="{BC020CB4-9F54-4585-97BD-7269FD182D8C}" name="Tower climb"/>
+    <tableColumn id="26" xr3:uid="{7D95AECF-5F33-44A3-BEA0-4C8B01E29D9D}" name="Climb time"/>
+    <tableColumn id="27" xr3:uid="{9FDD658C-7A69-4530-B727-8EF43F998459}" name="Driver skill"/>
+    <tableColumn id="28" xr3:uid="{780DF9CC-F01E-48DA-A888-9ABBEDFB041B}" name="Robot speed"/>
+    <tableColumn id="29" xr3:uid="{2B85B898-01AE-4BE8-AE40-67812E1FF499}" name="Shooting accuracy"/>
+    <tableColumn id="30" xr3:uid="{91185BD6-51BD-4D21-A8F3-0D0CF6C60F85}" name="Problems"/>
+    <tableColumn id="31" xr3:uid="{3CF4D09B-6235-4DAB-A676-A8FE40C8466F}" name="Minor fouls"/>
+    <tableColumn id="32" xr3:uid="{0E025CA8-68B9-4136-B2F5-58955BB8A866}" name="Major fouls"/>
+    <tableColumn id="33" xr3:uid="{76136306-993E-4C71-A1D0-C6B4B636A9FC}" name="Card"/>
+    <tableColumn id="34" xr3:uid="{7D73088F-0695-4088-9E64-EB635EB63B4E}" name="Pick?"/>
+    <tableColumn id="35" xr3:uid="{57556895-CAE8-4810-888E-20721A2C3D31}" name="Observations"/>
+    <tableColumn id="36" xr3:uid="{644DDB04-5018-4A95-8F6A-3E25F21E9AEC}" name="Auto pts" dataDxfId="6"/>
+    <tableColumn id="37" xr3:uid="{C72A519E-EA06-4DE3-A268-07C8B5580C32}" name="Teleop fuel pts" dataDxfId="5"/>
+    <tableColumn id="38" xr3:uid="{C7D65F17-E516-453B-BB66-F5BCC6ACC3B2}" name="Climb pts" dataDxfId="4"/>
+    <tableColumn id="39" xr3:uid="{D20FEAF3-09E1-4DE3-88C1-DEA4BF935BFF}" name="Total pts" dataDxfId="3"/>
+    <tableColumn id="40" xr3:uid="{2570BA35-A793-4C73-9BA7-B44DBC55C17E}" name="Submitted"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2013,7 +2043,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{944F1444-1D3A-4D04-9236-CB959DA8F463}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64426A21-F10F-4246-9480-039396E609BD}">
   <dimension ref="A1:J89"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2521,8 +2551,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{006304E6-79EA-409E-8DD3-9A455DD0C336}">
-  <dimension ref="A1:AN97"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C5AACAA-3229-4C4A-9153-483B2D1DF557}">
+  <dimension ref="A1:AN157"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.6328125" customWidth="1"/>
@@ -2694,13 +2724,13 @@
         <v>411</v>
       </c>
       <c r="K2">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O2" t="s">
         <v>412</v>
       </c>
       <c r="P2">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="Y2" t="s">
         <v>412</v>
@@ -2709,16 +2739,16 @@
         <v>413</v>
       </c>
       <c r="AJ2" s="9">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AK2" s="9">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="AL2" s="9">
         <v>0</v>
       </c>
       <c r="AM2" s="9">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="AN2" t="s">
         <v>414</v>
@@ -2750,13 +2780,13 @@
         <v>411</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O3" t="s">
         <v>412</v>
       </c>
       <c r="P3">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="Y3" t="s">
         <v>412</v>
@@ -2765,16 +2795,16 @@
         <v>413</v>
       </c>
       <c r="AJ3" s="9">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AK3" s="9">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="AL3" s="9">
         <v>0</v>
       </c>
       <c r="AM3" s="9">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="AN3" t="s">
         <v>414</v>
@@ -2806,13 +2836,13 @@
         <v>411</v>
       </c>
       <c r="K4">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="O4" t="s">
         <v>412</v>
       </c>
       <c r="P4">
-        <v>139</v>
+        <v>205</v>
       </c>
       <c r="Y4" t="s">
         <v>412</v>
@@ -2821,16 +2851,16 @@
         <v>413</v>
       </c>
       <c r="AJ4" s="9">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="AK4" s="9">
-        <v>139</v>
+        <v>205</v>
       </c>
       <c r="AL4" s="9">
         <v>0</v>
       </c>
       <c r="AM4" s="9">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="AN4" t="s">
         <v>414</v>
@@ -2862,13 +2892,13 @@
         <v>411</v>
       </c>
       <c r="K5">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O5" t="s">
         <v>412</v>
       </c>
       <c r="P5">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="Y5" t="s">
         <v>412</v>
@@ -2877,16 +2907,16 @@
         <v>413</v>
       </c>
       <c r="AJ5" s="9">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AK5" s="9">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="AL5" s="9">
         <v>0</v>
       </c>
       <c r="AM5" s="9">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AN5" t="s">
         <v>414</v>
@@ -2918,13 +2948,13 @@
         <v>411</v>
       </c>
       <c r="K6">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="O6" t="s">
         <v>412</v>
       </c>
       <c r="P6">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="Y6" t="s">
         <v>412</v>
@@ -2933,16 +2963,16 @@
         <v>413</v>
       </c>
       <c r="AJ6" s="9">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="AK6" s="9">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="AL6" s="9">
         <v>0</v>
       </c>
       <c r="AM6" s="9">
-        <v>265</v>
+        <v>315</v>
       </c>
       <c r="AN6" t="s">
         <v>414</v>
@@ -2974,13 +3004,13 @@
         <v>411</v>
       </c>
       <c r="K7">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="O7" t="s">
         <v>412</v>
       </c>
       <c r="P7">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="Y7" t="s">
         <v>412</v>
@@ -2989,16 +3019,16 @@
         <v>413</v>
       </c>
       <c r="AJ7" s="9">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="AK7" s="9">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="AL7" s="9">
         <v>0</v>
       </c>
       <c r="AM7" s="9">
-        <v>196</v>
+        <v>158</v>
       </c>
       <c r="AN7" t="s">
         <v>414</v>
@@ -3030,13 +3060,13 @@
         <v>411</v>
       </c>
       <c r="K8">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O8" t="s">
         <v>412</v>
       </c>
       <c r="P8">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Y8" t="s">
         <v>412</v>
@@ -3045,16 +3075,16 @@
         <v>413</v>
       </c>
       <c r="AJ8" s="9">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AK8" s="9">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AL8" s="9">
         <v>0</v>
       </c>
       <c r="AM8" s="9">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AN8" t="s">
         <v>416</v>
@@ -3086,13 +3116,13 @@
         <v>411</v>
       </c>
       <c r="K9">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="O9" t="s">
         <v>412</v>
       </c>
       <c r="P9">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="Y9" t="s">
         <v>412</v>
@@ -3101,16 +3131,16 @@
         <v>413</v>
       </c>
       <c r="AJ9" s="9">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="AK9" s="9">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="AL9" s="9">
         <v>0</v>
       </c>
       <c r="AM9" s="9">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="AN9" t="s">
         <v>416</v>
@@ -3142,13 +3172,13 @@
         <v>411</v>
       </c>
       <c r="K10">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="O10" t="s">
         <v>412</v>
       </c>
       <c r="P10">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="Y10" t="s">
         <v>412</v>
@@ -3157,16 +3187,16 @@
         <v>413</v>
       </c>
       <c r="AJ10" s="9">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="AK10" s="9">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="AL10" s="9">
         <v>0</v>
       </c>
       <c r="AM10" s="9">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="AN10" t="s">
         <v>416</v>
@@ -3198,13 +3228,13 @@
         <v>411</v>
       </c>
       <c r="K11">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="O11" t="s">
         <v>412</v>
       </c>
       <c r="P11">
-        <v>125</v>
+        <v>169</v>
       </c>
       <c r="Y11" t="s">
         <v>412</v>
@@ -3213,16 +3243,16 @@
         <v>413</v>
       </c>
       <c r="AJ11" s="9">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AK11" s="9">
-        <v>125</v>
+        <v>169</v>
       </c>
       <c r="AL11" s="9">
         <v>0</v>
       </c>
       <c r="AM11" s="9">
-        <v>162</v>
+        <v>213</v>
       </c>
       <c r="AN11" t="s">
         <v>416</v>
@@ -3254,13 +3284,13 @@
         <v>411</v>
       </c>
       <c r="K12">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O12" t="s">
         <v>412</v>
       </c>
       <c r="P12">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="s">
         <v>412</v>
@@ -3269,16 +3299,16 @@
         <v>413</v>
       </c>
       <c r="AJ12" s="9">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AK12" s="9">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="AL12" s="9">
         <v>0</v>
       </c>
       <c r="AM12" s="9">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="AN12" t="s">
         <v>416</v>
@@ -3310,13 +3340,13 @@
         <v>411</v>
       </c>
       <c r="K13">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O13" t="s">
         <v>412</v>
       </c>
       <c r="P13">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="Y13" t="s">
         <v>412</v>
@@ -3325,16 +3355,16 @@
         <v>413</v>
       </c>
       <c r="AJ13" s="9">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AK13" s="9">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="AL13" s="9">
         <v>0</v>
       </c>
       <c r="AM13" s="9">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="AN13" t="s">
         <v>416</v>
@@ -3366,13 +3396,13 @@
         <v>411</v>
       </c>
       <c r="K14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O14" t="s">
         <v>412</v>
       </c>
       <c r="P14">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Y14" t="s">
         <v>412</v>
@@ -3381,16 +3411,16 @@
         <v>413</v>
       </c>
       <c r="AJ14" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK14" s="9">
+        <v>38</v>
+      </c>
+      <c r="AL14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="9">
         <v>39</v>
-      </c>
-      <c r="AL14" s="9">
-        <v>0</v>
-      </c>
-      <c r="AM14" s="9">
-        <v>41</v>
       </c>
       <c r="AN14" t="s">
         <v>417</v>
@@ -3422,13 +3452,13 @@
         <v>411</v>
       </c>
       <c r="K15">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O15" t="s">
         <v>412</v>
       </c>
       <c r="P15">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="Y15" t="s">
         <v>412</v>
@@ -3437,16 +3467,16 @@
         <v>413</v>
       </c>
       <c r="AJ15" s="9">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="AK15" s="9">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="AL15" s="9">
         <v>0</v>
       </c>
       <c r="AM15" s="9">
-        <v>265</v>
+        <v>286</v>
       </c>
       <c r="AN15" t="s">
         <v>417</v>
@@ -3478,13 +3508,13 @@
         <v>411</v>
       </c>
       <c r="K16">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="O16" t="s">
         <v>412</v>
       </c>
       <c r="P16">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="Y16" t="s">
         <v>412</v>
@@ -3493,16 +3523,16 @@
         <v>413</v>
       </c>
       <c r="AJ16" s="9">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AK16" s="9">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="AL16" s="9">
         <v>0</v>
       </c>
       <c r="AM16" s="9">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="AN16" t="s">
         <v>417</v>
@@ -3534,13 +3564,13 @@
         <v>411</v>
       </c>
       <c r="K17">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="O17" t="s">
         <v>412</v>
       </c>
       <c r="P17">
-        <v>66</v>
+        <v>109</v>
       </c>
       <c r="Y17" t="s">
         <v>412</v>
@@ -3549,16 +3579,16 @@
         <v>413</v>
       </c>
       <c r="AJ17" s="9">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="AK17" s="9">
-        <v>66</v>
+        <v>109</v>
       </c>
       <c r="AL17" s="9">
         <v>0</v>
       </c>
       <c r="AM17" s="9">
-        <v>92</v>
+        <v>146</v>
       </c>
       <c r="AN17" t="s">
         <v>417</v>
@@ -3590,13 +3620,13 @@
         <v>411</v>
       </c>
       <c r="K18">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="O18" t="s">
         <v>412</v>
       </c>
       <c r="P18">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Y18" t="s">
         <v>412</v>
@@ -3605,16 +3635,16 @@
         <v>413</v>
       </c>
       <c r="AJ18" s="9">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="AK18" s="9">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AL18" s="9">
         <v>0</v>
       </c>
       <c r="AM18" s="9">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="AN18" t="s">
         <v>417</v>
@@ -3646,13 +3676,13 @@
         <v>411</v>
       </c>
       <c r="K19">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="O19" t="s">
         <v>412</v>
       </c>
       <c r="P19">
-        <v>86</v>
+        <v>44</v>
       </c>
       <c r="Y19" t="s">
         <v>412</v>
@@ -3661,16 +3691,16 @@
         <v>413</v>
       </c>
       <c r="AJ19" s="9">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="AK19" s="9">
-        <v>86</v>
+        <v>44</v>
       </c>
       <c r="AL19" s="9">
         <v>0</v>
       </c>
       <c r="AM19" s="9">
-        <v>134</v>
+        <v>73</v>
       </c>
       <c r="AN19" t="s">
         <v>417</v>
@@ -3702,13 +3732,13 @@
         <v>411</v>
       </c>
       <c r="K20">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O20" t="s">
         <v>412</v>
       </c>
       <c r="P20">
-        <v>55</v>
+        <v>108</v>
       </c>
       <c r="Y20" t="s">
         <v>412</v>
@@ -3717,16 +3747,16 @@
         <v>413</v>
       </c>
       <c r="AJ20" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK20" s="9">
-        <v>55</v>
+        <v>108</v>
       </c>
       <c r="AL20" s="9">
         <v>0</v>
       </c>
       <c r="AM20" s="9">
-        <v>71</v>
+        <v>123</v>
       </c>
       <c r="AN20" t="s">
         <v>418</v>
@@ -3758,13 +3788,13 @@
         <v>411</v>
       </c>
       <c r="K21">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="O21" t="s">
         <v>412</v>
       </c>
       <c r="P21">
-        <v>86</v>
+        <v>13</v>
       </c>
       <c r="Y21" t="s">
         <v>412</v>
@@ -3773,16 +3803,16 @@
         <v>413</v>
       </c>
       <c r="AJ21" s="9">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="AK21" s="9">
-        <v>86</v>
+        <v>13</v>
       </c>
       <c r="AL21" s="9">
         <v>0</v>
       </c>
       <c r="AM21" s="9">
-        <v>110</v>
+        <v>22</v>
       </c>
       <c r="AN21" t="s">
         <v>418</v>
@@ -3814,13 +3844,13 @@
         <v>411</v>
       </c>
       <c r="K22">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="O22" t="s">
         <v>412</v>
       </c>
       <c r="P22">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="Y22" t="s">
         <v>412</v>
@@ -3829,16 +3859,16 @@
         <v>413</v>
       </c>
       <c r="AJ22" s="9">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="AK22" s="9">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="AL22" s="9">
         <v>0</v>
       </c>
       <c r="AM22" s="9">
-        <v>114</v>
+        <v>150</v>
       </c>
       <c r="AN22" t="s">
         <v>418</v>
@@ -3870,13 +3900,13 @@
         <v>411</v>
       </c>
       <c r="K23">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O23" t="s">
         <v>412</v>
       </c>
       <c r="P23">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="Y23" t="s">
         <v>412</v>
@@ -3885,16 +3915,16 @@
         <v>413</v>
       </c>
       <c r="AJ23" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AK23" s="9">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="AL23" s="9">
         <v>0</v>
       </c>
       <c r="AM23" s="9">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="AN23" t="s">
         <v>418</v>
@@ -3926,13 +3956,13 @@
         <v>411</v>
       </c>
       <c r="K24">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="O24" t="s">
         <v>412</v>
       </c>
       <c r="P24">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="Y24" t="s">
         <v>412</v>
@@ -3941,16 +3971,16 @@
         <v>413</v>
       </c>
       <c r="AJ24" s="9">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AK24" s="9">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="AL24" s="9">
         <v>0</v>
       </c>
       <c r="AM24" s="9">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="AN24" t="s">
         <v>418</v>
@@ -3982,13 +4012,13 @@
         <v>411</v>
       </c>
       <c r="K25">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="O25" t="s">
         <v>412</v>
       </c>
       <c r="P25">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="Y25" t="s">
         <v>412</v>
@@ -3997,16 +4027,16 @@
         <v>413</v>
       </c>
       <c r="AJ25" s="9">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AK25" s="9">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="AL25" s="9">
         <v>0</v>
       </c>
       <c r="AM25" s="9">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="AN25" t="s">
         <v>418</v>
@@ -4038,13 +4068,13 @@
         <v>411</v>
       </c>
       <c r="K26">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O26" t="s">
         <v>412</v>
       </c>
       <c r="P26">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Y26" t="s">
         <v>412</v>
@@ -4053,16 +4083,16 @@
         <v>413</v>
       </c>
       <c r="AJ26" s="9">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AK26" s="9">
+        <v>53</v>
+      </c>
+      <c r="AL26" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM26" s="9">
         <v>55</v>
-      </c>
-      <c r="AL26" s="9">
-        <v>0</v>
-      </c>
-      <c r="AM26" s="9">
-        <v>62</v>
       </c>
       <c r="AN26" t="s">
         <v>421</v>
@@ -4100,7 +4130,7 @@
         <v>412</v>
       </c>
       <c r="P27">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="Y27" t="s">
         <v>412</v>
@@ -4112,13 +4142,13 @@
         <v>1</v>
       </c>
       <c r="AK27" s="9">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="AL27" s="9">
         <v>0</v>
       </c>
       <c r="AM27" s="9">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="AN27" t="s">
         <v>421</v>
@@ -4150,13 +4180,13 @@
         <v>411</v>
       </c>
       <c r="K28">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="O28" t="s">
         <v>412</v>
       </c>
       <c r="P28">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="Y28" t="s">
         <v>412</v>
@@ -4165,16 +4195,16 @@
         <v>413</v>
       </c>
       <c r="AJ28" s="9">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AK28" s="9">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="AL28" s="9">
         <v>0</v>
       </c>
       <c r="AM28" s="9">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="AN28" t="s">
         <v>421</v>
@@ -4206,13 +4236,13 @@
         <v>411</v>
       </c>
       <c r="K29">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="O29" t="s">
         <v>412</v>
       </c>
       <c r="P29">
-        <v>114</v>
+        <v>61</v>
       </c>
       <c r="Y29" t="s">
         <v>412</v>
@@ -4221,16 +4251,16 @@
         <v>413</v>
       </c>
       <c r="AJ29" s="9">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="AK29" s="9">
-        <v>114</v>
+        <v>61</v>
       </c>
       <c r="AL29" s="9">
         <v>0</v>
       </c>
       <c r="AM29" s="9">
-        <v>176</v>
+        <v>99</v>
       </c>
       <c r="AN29" t="s">
         <v>421</v>
@@ -4262,13 +4292,13 @@
         <v>411</v>
       </c>
       <c r="K30">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O30" t="s">
         <v>412</v>
       </c>
       <c r="P30">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="Y30" t="s">
         <v>412</v>
@@ -4277,16 +4307,16 @@
         <v>413</v>
       </c>
       <c r="AJ30" s="9">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AK30" s="9">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="AL30" s="9">
         <v>0</v>
       </c>
       <c r="AM30" s="9">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="AN30" t="s">
         <v>421</v>
@@ -4318,13 +4348,13 @@
         <v>411</v>
       </c>
       <c r="K31">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="O31" t="s">
         <v>412</v>
       </c>
       <c r="P31">
-        <v>79</v>
+        <v>130</v>
       </c>
       <c r="Y31" t="s">
         <v>412</v>
@@ -4333,16 +4363,16 @@
         <v>413</v>
       </c>
       <c r="AJ31" s="9">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="AK31" s="9">
-        <v>79</v>
+        <v>130</v>
       </c>
       <c r="AL31" s="9">
         <v>0</v>
       </c>
       <c r="AM31" s="9">
-        <v>94</v>
+        <v>175</v>
       </c>
       <c r="AN31" t="s">
         <v>421</v>
@@ -4374,13 +4404,13 @@
         <v>411</v>
       </c>
       <c r="K32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O32" t="s">
         <v>412</v>
       </c>
       <c r="P32">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="Y32" t="s">
         <v>412</v>
@@ -4389,16 +4419,16 @@
         <v>413</v>
       </c>
       <c r="AJ32" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK32" s="9">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="AL32" s="9">
         <v>0</v>
       </c>
       <c r="AM32" s="9">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="AN32" t="s">
         <v>422</v>
@@ -4430,13 +4460,13 @@
         <v>411</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O33" t="s">
         <v>412</v>
       </c>
       <c r="P33">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="Y33" t="s">
         <v>412</v>
@@ -4445,16 +4475,16 @@
         <v>413</v>
       </c>
       <c r="AJ33" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK33" s="9">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="AL33" s="9">
         <v>0</v>
       </c>
       <c r="AM33" s="9">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="AN33" t="s">
         <v>422</v>
@@ -4492,7 +4522,7 @@
         <v>412</v>
       </c>
       <c r="P34">
-        <v>98</v>
+        <v>55</v>
       </c>
       <c r="Y34" t="s">
         <v>412</v>
@@ -4504,13 +4534,13 @@
         <v>10</v>
       </c>
       <c r="AK34" s="9">
-        <v>98</v>
+        <v>55</v>
       </c>
       <c r="AL34" s="9">
         <v>0</v>
       </c>
       <c r="AM34" s="9">
-        <v>108</v>
+        <v>65</v>
       </c>
       <c r="AN34" t="s">
         <v>422</v>
@@ -4542,13 +4572,13 @@
         <v>411</v>
       </c>
       <c r="K35">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="O35" t="s">
         <v>412</v>
       </c>
       <c r="P35">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="Y35" t="s">
         <v>412</v>
@@ -4557,16 +4587,16 @@
         <v>413</v>
       </c>
       <c r="AJ35" s="9">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AK35" s="9">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="AL35" s="9">
         <v>0</v>
       </c>
       <c r="AM35" s="9">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="AN35" t="s">
         <v>422</v>
@@ -4598,13 +4628,13 @@
         <v>411</v>
       </c>
       <c r="K36">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O36" t="s">
         <v>412</v>
       </c>
       <c r="P36">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Y36" t="s">
         <v>412</v>
@@ -4613,16 +4643,16 @@
         <v>413</v>
       </c>
       <c r="AJ36" s="9">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AK36" s="9">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AL36" s="9">
         <v>0</v>
       </c>
       <c r="AM36" s="9">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AN36" t="s">
         <v>422</v>
@@ -4654,13 +4684,13 @@
         <v>411</v>
       </c>
       <c r="K37">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O37" t="s">
         <v>412</v>
       </c>
       <c r="P37">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Y37" t="s">
         <v>412</v>
@@ -4669,16 +4699,16 @@
         <v>413</v>
       </c>
       <c r="AJ37" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AK37" s="9">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AL37" s="9">
         <v>0</v>
       </c>
       <c r="AM37" s="9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AN37" t="s">
         <v>422</v>
@@ -4716,7 +4746,7 @@
         <v>412</v>
       </c>
       <c r="P38">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="Y38" t="s">
         <v>412</v>
@@ -4728,13 +4758,13 @@
         <v>3</v>
       </c>
       <c r="AK38" s="9">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="AL38" s="9">
         <v>0</v>
       </c>
       <c r="AM38" s="9">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="AN38" t="s">
         <v>424</v>
@@ -4766,13 +4796,13 @@
         <v>411</v>
       </c>
       <c r="K39">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="O39" t="s">
         <v>412</v>
       </c>
       <c r="P39">
-        <v>88</v>
+        <v>160</v>
       </c>
       <c r="Y39" t="s">
         <v>412</v>
@@ -4781,16 +4811,16 @@
         <v>413</v>
       </c>
       <c r="AJ39" s="9">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="AK39" s="9">
-        <v>88</v>
+        <v>160</v>
       </c>
       <c r="AL39" s="9">
         <v>0</v>
       </c>
       <c r="AM39" s="9">
-        <v>96</v>
+        <v>177</v>
       </c>
       <c r="AN39" t="s">
         <v>424</v>
@@ -4822,13 +4852,13 @@
         <v>411</v>
       </c>
       <c r="K40">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="O40" t="s">
         <v>412</v>
       </c>
       <c r="P40">
-        <v>174</v>
+        <v>151</v>
       </c>
       <c r="Y40" t="s">
         <v>412</v>
@@ -4837,16 +4867,16 @@
         <v>413</v>
       </c>
       <c r="AJ40" s="9">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AK40" s="9">
-        <v>174</v>
+        <v>151</v>
       </c>
       <c r="AL40" s="9">
         <v>0</v>
       </c>
       <c r="AM40" s="9">
-        <v>187</v>
+        <v>155</v>
       </c>
       <c r="AN40" t="s">
         <v>424</v>
@@ -4878,13 +4908,13 @@
         <v>411</v>
       </c>
       <c r="K41">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="O41" t="s">
         <v>412</v>
       </c>
       <c r="P41">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="Y41" t="s">
         <v>412</v>
@@ -4893,16 +4923,16 @@
         <v>413</v>
       </c>
       <c r="AJ41" s="9">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="AK41" s="9">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="AL41" s="9">
         <v>0</v>
       </c>
       <c r="AM41" s="9">
-        <v>116</v>
+        <v>84</v>
       </c>
       <c r="AN41" t="s">
         <v>424</v>
@@ -4934,13 +4964,13 @@
         <v>411</v>
       </c>
       <c r="K42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O42" t="s">
         <v>412</v>
       </c>
       <c r="P42">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Y42" t="s">
         <v>412</v>
@@ -4949,16 +4979,16 @@
         <v>413</v>
       </c>
       <c r="AJ42" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK42" s="9">
+        <v>34</v>
+      </c>
+      <c r="AL42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="9">
         <v>35</v>
-      </c>
-      <c r="AL42" s="9">
-        <v>0</v>
-      </c>
-      <c r="AM42" s="9">
-        <v>37</v>
       </c>
       <c r="AN42" t="s">
         <v>424</v>
@@ -4990,13 +5020,13 @@
         <v>411</v>
       </c>
       <c r="K43">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="O43" t="s">
         <v>412</v>
       </c>
       <c r="P43">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="Y43" t="s">
         <v>412</v>
@@ -5005,16 +5035,16 @@
         <v>413</v>
       </c>
       <c r="AJ43" s="9">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="AK43" s="9">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="AL43" s="9">
         <v>0</v>
       </c>
       <c r="AM43" s="9">
-        <v>97</v>
+        <v>131</v>
       </c>
       <c r="AN43" t="s">
         <v>424</v>
@@ -5046,13 +5076,13 @@
         <v>411</v>
       </c>
       <c r="K44">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="O44" t="s">
         <v>412</v>
       </c>
       <c r="P44">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="Y44" t="s">
         <v>412</v>
@@ -5061,16 +5091,16 @@
         <v>413</v>
       </c>
       <c r="AJ44" s="9">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="AK44" s="9">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="AL44" s="9">
         <v>0</v>
       </c>
       <c r="AM44" s="9">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="AN44" t="s">
         <v>425</v>
@@ -5102,13 +5132,13 @@
         <v>411</v>
       </c>
       <c r="K45">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O45" t="s">
         <v>412</v>
       </c>
       <c r="P45">
-        <v>222</v>
+        <v>258</v>
       </c>
       <c r="Y45" t="s">
         <v>412</v>
@@ -5117,16 +5147,16 @@
         <v>413</v>
       </c>
       <c r="AJ45" s="9">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AK45" s="9">
-        <v>222</v>
+        <v>258</v>
       </c>
       <c r="AL45" s="9">
         <v>0</v>
       </c>
       <c r="AM45" s="9">
-        <v>269</v>
+        <v>307</v>
       </c>
       <c r="AN45" t="s">
         <v>425</v>
@@ -5158,13 +5188,13 @@
         <v>411</v>
       </c>
       <c r="K46">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="O46" t="s">
         <v>412</v>
       </c>
       <c r="P46">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="Y46" t="s">
         <v>412</v>
@@ -5173,16 +5203,16 @@
         <v>413</v>
       </c>
       <c r="AJ46" s="9">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="AK46" s="9">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="AL46" s="9">
         <v>0</v>
       </c>
       <c r="AM46" s="9">
-        <v>188</v>
+        <v>113</v>
       </c>
       <c r="AN46" t="s">
         <v>425</v>
@@ -5214,13 +5244,13 @@
         <v>411</v>
       </c>
       <c r="K47">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="O47" t="s">
         <v>412</v>
       </c>
       <c r="P47">
-        <v>140</v>
+        <v>193</v>
       </c>
       <c r="Y47" t="s">
         <v>412</v>
@@ -5229,16 +5259,16 @@
         <v>413</v>
       </c>
       <c r="AJ47" s="9">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="AK47" s="9">
-        <v>140</v>
+        <v>193</v>
       </c>
       <c r="AL47" s="9">
         <v>0</v>
       </c>
       <c r="AM47" s="9">
-        <v>192</v>
+        <v>238</v>
       </c>
       <c r="AN47" t="s">
         <v>425</v>
@@ -5270,13 +5300,13 @@
         <v>411</v>
       </c>
       <c r="K48">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="O48" t="s">
         <v>412</v>
       </c>
       <c r="P48">
-        <v>110</v>
+        <v>52</v>
       </c>
       <c r="Y48" t="s">
         <v>412</v>
@@ -5285,16 +5315,16 @@
         <v>413</v>
       </c>
       <c r="AJ48" s="9">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="AK48" s="9">
-        <v>110</v>
+        <v>52</v>
       </c>
       <c r="AL48" s="9">
         <v>0</v>
       </c>
       <c r="AM48" s="9">
-        <v>129</v>
+        <v>81</v>
       </c>
       <c r="AN48" t="s">
         <v>425</v>
@@ -5326,13 +5356,13 @@
         <v>411</v>
       </c>
       <c r="K49">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O49" t="s">
         <v>412</v>
       </c>
       <c r="P49">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="Y49" t="s">
         <v>412</v>
@@ -5341,16 +5371,16 @@
         <v>413</v>
       </c>
       <c r="AJ49" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AK49" s="9">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="AL49" s="9">
         <v>0</v>
       </c>
       <c r="AM49" s="9">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="AN49" t="s">
         <v>425</v>
@@ -5382,13 +5412,13 @@
         <v>411</v>
       </c>
       <c r="K50">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="O50" t="s">
         <v>412</v>
       </c>
       <c r="P50">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="Y50" t="s">
         <v>412</v>
@@ -5397,16 +5427,16 @@
         <v>413</v>
       </c>
       <c r="AJ50" s="9">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AK50" s="9">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="AL50" s="9">
         <v>0</v>
       </c>
       <c r="AM50" s="9">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="AN50" t="s">
         <v>426</v>
@@ -5438,13 +5468,13 @@
         <v>411</v>
       </c>
       <c r="K51">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="O51" t="s">
         <v>412</v>
       </c>
       <c r="P51">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="Y51" t="s">
         <v>412</v>
@@ -5453,16 +5483,16 @@
         <v>413</v>
       </c>
       <c r="AJ51" s="9">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AK51" s="9">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="AL51" s="9">
         <v>0</v>
       </c>
       <c r="AM51" s="9">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="AN51" t="s">
         <v>426</v>
@@ -5500,7 +5530,7 @@
         <v>412</v>
       </c>
       <c r="P52">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="Y52" t="s">
         <v>412</v>
@@ -5512,13 +5542,13 @@
         <v>1</v>
       </c>
       <c r="AK52" s="9">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="AL52" s="9">
         <v>0</v>
       </c>
       <c r="AM52" s="9">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="AN52" t="s">
         <v>426</v>
@@ -5550,13 +5580,13 @@
         <v>411</v>
       </c>
       <c r="K53">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="O53" t="s">
         <v>412</v>
       </c>
       <c r="P53">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="Y53" t="s">
         <v>412</v>
@@ -5565,16 +5595,16 @@
         <v>413</v>
       </c>
       <c r="AJ53" s="9">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AK53" s="9">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AL53" s="9">
         <v>0</v>
       </c>
       <c r="AM53" s="9">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AN53" t="s">
         <v>426</v>
@@ -5606,13 +5636,13 @@
         <v>411</v>
       </c>
       <c r="K54">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="O54" t="s">
         <v>412</v>
       </c>
       <c r="P54">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="Y54" t="s">
         <v>412</v>
@@ -5621,16 +5651,16 @@
         <v>413</v>
       </c>
       <c r="AJ54" s="9">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AK54" s="9">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="AL54" s="9">
         <v>0</v>
       </c>
       <c r="AM54" s="9">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AN54" t="s">
         <v>426</v>
@@ -5662,13 +5692,13 @@
         <v>411</v>
       </c>
       <c r="K55">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O55" t="s">
         <v>412</v>
       </c>
       <c r="P55">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Y55" t="s">
         <v>412</v>
@@ -5677,16 +5707,16 @@
         <v>413</v>
       </c>
       <c r="AJ55" s="9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AK55" s="9">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AL55" s="9">
         <v>0</v>
       </c>
       <c r="AM55" s="9">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AN55" t="s">
         <v>426</v>
@@ -5718,13 +5748,13 @@
         <v>411</v>
       </c>
       <c r="K56">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O56" t="s">
         <v>412</v>
       </c>
       <c r="P56">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="Y56" t="s">
         <v>412</v>
@@ -5733,16 +5763,16 @@
         <v>413</v>
       </c>
       <c r="AJ56" s="9">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AK56" s="9">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="AL56" s="9">
         <v>0</v>
       </c>
       <c r="AM56" s="9">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="AN56" t="s">
         <v>427</v>
@@ -5780,7 +5810,7 @@
         <v>412</v>
       </c>
       <c r="P57">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="Y57" t="s">
         <v>412</v>
@@ -5792,13 +5822,13 @@
         <v>1</v>
       </c>
       <c r="AK57" s="9">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="AL57" s="9">
         <v>0</v>
       </c>
       <c r="AM57" s="9">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="AN57" t="s">
         <v>427</v>
@@ -5830,13 +5860,13 @@
         <v>411</v>
       </c>
       <c r="K58">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="O58" t="s">
         <v>412</v>
       </c>
       <c r="P58">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="Y58" t="s">
         <v>412</v>
@@ -5845,16 +5875,16 @@
         <v>413</v>
       </c>
       <c r="AJ58" s="9">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AK58" s="9">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="AL58" s="9">
         <v>0</v>
       </c>
       <c r="AM58" s="9">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="AN58" t="s">
         <v>427</v>
@@ -5886,13 +5916,13 @@
         <v>411</v>
       </c>
       <c r="K59">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="O59" t="s">
         <v>412</v>
       </c>
       <c r="P59">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="Y59" t="s">
         <v>412</v>
@@ -5901,16 +5931,16 @@
         <v>413</v>
       </c>
       <c r="AJ59" s="9">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="AK59" s="9">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="AL59" s="9">
         <v>0</v>
       </c>
       <c r="AM59" s="9">
-        <v>123</v>
+        <v>76</v>
       </c>
       <c r="AN59" t="s">
         <v>427</v>
@@ -5942,13 +5972,13 @@
         <v>411</v>
       </c>
       <c r="K60">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="O60" t="s">
         <v>412</v>
       </c>
       <c r="P60">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="Y60" t="s">
         <v>412</v>
@@ -5957,16 +5987,16 @@
         <v>413</v>
       </c>
       <c r="AJ60" s="9">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AK60" s="9">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="AL60" s="9">
         <v>0</v>
       </c>
       <c r="AM60" s="9">
-        <v>206</v>
+        <v>187</v>
       </c>
       <c r="AN60" t="s">
         <v>427</v>
@@ -5998,13 +6028,13 @@
         <v>411</v>
       </c>
       <c r="K61">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="O61" t="s">
         <v>412</v>
       </c>
       <c r="P61">
-        <v>53</v>
+        <v>114</v>
       </c>
       <c r="Y61" t="s">
         <v>412</v>
@@ -6013,16 +6043,16 @@
         <v>413</v>
       </c>
       <c r="AJ61" s="9">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AK61" s="9">
-        <v>53</v>
+        <v>114</v>
       </c>
       <c r="AL61" s="9">
         <v>0</v>
       </c>
       <c r="AM61" s="9">
-        <v>69</v>
+        <v>135</v>
       </c>
       <c r="AN61" t="s">
         <v>427</v>
@@ -6054,13 +6084,13 @@
         <v>411</v>
       </c>
       <c r="K62">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="O62" t="s">
         <v>412</v>
       </c>
       <c r="P62">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="Y62" t="s">
         <v>412</v>
@@ -6069,16 +6099,16 @@
         <v>413</v>
       </c>
       <c r="AJ62" s="9">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="AK62" s="9">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="AL62" s="9">
         <v>0</v>
       </c>
       <c r="AM62" s="9">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="AN62" t="s">
         <v>428</v>
@@ -6110,13 +6140,13 @@
         <v>411</v>
       </c>
       <c r="K63">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="O63" t="s">
         <v>412</v>
       </c>
       <c r="P63">
-        <v>162</v>
+        <v>136</v>
       </c>
       <c r="Y63" t="s">
         <v>412</v>
@@ -6125,16 +6155,16 @@
         <v>413</v>
       </c>
       <c r="AJ63" s="9">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="AK63" s="9">
+        <v>136</v>
+      </c>
+      <c r="AL63" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM63" s="9">
         <v>162</v>
-      </c>
-      <c r="AL63" s="9">
-        <v>0</v>
-      </c>
-      <c r="AM63" s="9">
-        <v>193</v>
       </c>
       <c r="AN63" t="s">
         <v>428</v>
@@ -6166,13 +6196,13 @@
         <v>411</v>
       </c>
       <c r="K64">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="O64" t="s">
         <v>412</v>
       </c>
       <c r="P64">
-        <v>206</v>
+        <v>254</v>
       </c>
       <c r="Y64" t="s">
         <v>412</v>
@@ -6181,16 +6211,16 @@
         <v>413</v>
       </c>
       <c r="AJ64" s="9">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="AK64" s="9">
-        <v>206</v>
+        <v>254</v>
       </c>
       <c r="AL64" s="9">
         <v>0</v>
       </c>
       <c r="AM64" s="9">
-        <v>272</v>
+        <v>312</v>
       </c>
       <c r="AN64" t="s">
         <v>428</v>
@@ -6222,13 +6252,13 @@
         <v>411</v>
       </c>
       <c r="K65">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="O65" t="s">
         <v>412</v>
       </c>
       <c r="P65">
-        <v>54</v>
+        <v>107</v>
       </c>
       <c r="Y65" t="s">
         <v>412</v>
@@ -6237,16 +6267,16 @@
         <v>413</v>
       </c>
       <c r="AJ65" s="9">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="AK65" s="9">
-        <v>54</v>
+        <v>107</v>
       </c>
       <c r="AL65" s="9">
         <v>0</v>
       </c>
       <c r="AM65" s="9">
-        <v>79</v>
+        <v>152</v>
       </c>
       <c r="AN65" t="s">
         <v>428</v>
@@ -6278,13 +6308,13 @@
         <v>411</v>
       </c>
       <c r="K66">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="O66" t="s">
         <v>412</v>
       </c>
       <c r="P66">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="Y66" t="s">
         <v>412</v>
@@ -6293,16 +6323,16 @@
         <v>413</v>
       </c>
       <c r="AJ66" s="9">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="AK66" s="9">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="AL66" s="9">
         <v>0</v>
       </c>
       <c r="AM66" s="9">
-        <v>96</v>
+        <v>27</v>
       </c>
       <c r="AN66" t="s">
         <v>428</v>
@@ -6334,13 +6364,13 @@
         <v>411</v>
       </c>
       <c r="K67">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O67" t="s">
         <v>412</v>
       </c>
       <c r="P67">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Y67" t="s">
         <v>412</v>
@@ -6349,16 +6379,16 @@
         <v>413</v>
       </c>
       <c r="AJ67" s="9">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AK67" s="9">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="AL67" s="9">
         <v>0</v>
       </c>
       <c r="AM67" s="9">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="AN67" t="s">
         <v>428</v>
@@ -6390,13 +6420,13 @@
         <v>411</v>
       </c>
       <c r="K68">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O68" t="s">
         <v>412</v>
       </c>
       <c r="P68">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="Y68" t="s">
         <v>412</v>
@@ -6405,16 +6435,16 @@
         <v>413</v>
       </c>
       <c r="AJ68" s="9">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AK68" s="9">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AL68" s="9">
         <v>0</v>
       </c>
       <c r="AM68" s="9">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="AN68" t="s">
         <v>429</v>
@@ -6446,13 +6476,13 @@
         <v>411</v>
       </c>
       <c r="K69">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="O69" t="s">
         <v>412</v>
       </c>
       <c r="P69">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="Y69" t="s">
         <v>412</v>
@@ -6461,16 +6491,16 @@
         <v>413</v>
       </c>
       <c r="AJ69" s="9">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AK69" s="9">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="AL69" s="9">
         <v>0</v>
       </c>
       <c r="AM69" s="9">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="AN69" t="s">
         <v>429</v>
@@ -6508,7 +6538,7 @@
         <v>412</v>
       </c>
       <c r="P70">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="Y70" t="s">
         <v>412</v>
@@ -6520,13 +6550,13 @@
         <v>28</v>
       </c>
       <c r="AK70" s="9">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="AL70" s="9">
         <v>0</v>
       </c>
       <c r="AM70" s="9">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="AN70" t="s">
         <v>429</v>
@@ -6558,13 +6588,13 @@
         <v>411</v>
       </c>
       <c r="K71">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="O71" t="s">
         <v>412</v>
       </c>
       <c r="P71">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="Y71" t="s">
         <v>412</v>
@@ -6573,16 +6603,16 @@
         <v>413</v>
       </c>
       <c r="AJ71" s="9">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="AK71" s="9">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="AL71" s="9">
         <v>0</v>
       </c>
       <c r="AM71" s="9">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="AN71" t="s">
         <v>429</v>
@@ -6620,7 +6650,7 @@
         <v>412</v>
       </c>
       <c r="P72">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="Y72" t="s">
         <v>412</v>
@@ -6632,13 +6662,13 @@
         <v>1</v>
       </c>
       <c r="AK72" s="9">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="AL72" s="9">
         <v>0</v>
       </c>
       <c r="AM72" s="9">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="AN72" t="s">
         <v>429</v>
@@ -6670,13 +6700,13 @@
         <v>411</v>
       </c>
       <c r="K73">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="O73" t="s">
         <v>412</v>
       </c>
       <c r="P73">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="Y73" t="s">
         <v>412</v>
@@ -6685,16 +6715,16 @@
         <v>413</v>
       </c>
       <c r="AJ73" s="9">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="AK73" s="9">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="AL73" s="9">
         <v>0</v>
       </c>
       <c r="AM73" s="9">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="AN73" t="s">
         <v>429</v>
@@ -6726,13 +6756,13 @@
         <v>411</v>
       </c>
       <c r="K74">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O74" t="s">
         <v>412</v>
       </c>
       <c r="P74">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="Y74" t="s">
         <v>412</v>
@@ -6741,16 +6771,16 @@
         <v>413</v>
       </c>
       <c r="AJ74" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK74" s="9">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="AL74" s="9">
         <v>0</v>
       </c>
       <c r="AM74" s="9">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="AN74" t="s">
         <v>430</v>
@@ -6782,13 +6812,13 @@
         <v>411</v>
       </c>
       <c r="K75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O75" t="s">
         <v>412</v>
       </c>
       <c r="P75">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y75" t="s">
         <v>412</v>
@@ -6797,16 +6827,16 @@
         <v>413</v>
       </c>
       <c r="AJ75" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK75" s="9">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AL75" s="9">
         <v>0</v>
       </c>
       <c r="AM75" s="9">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AN75" t="s">
         <v>430</v>
@@ -6838,13 +6868,13 @@
         <v>411</v>
       </c>
       <c r="K76">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O76" t="s">
         <v>412</v>
       </c>
       <c r="P76">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="Y76" t="s">
         <v>412</v>
@@ -6853,16 +6883,16 @@
         <v>413</v>
       </c>
       <c r="AJ76" s="9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AK76" s="9">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="AL76" s="9">
         <v>0</v>
       </c>
       <c r="AM76" s="9">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="AN76" t="s">
         <v>430</v>
@@ -6894,13 +6924,13 @@
         <v>411</v>
       </c>
       <c r="K77">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O77" t="s">
         <v>412</v>
       </c>
       <c r="P77">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="Y77" t="s">
         <v>412</v>
@@ -6909,16 +6939,16 @@
         <v>413</v>
       </c>
       <c r="AJ77" s="9">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AK77" s="9">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="AL77" s="9">
         <v>0</v>
       </c>
       <c r="AM77" s="9">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="AN77" t="s">
         <v>430</v>
@@ -6956,7 +6986,7 @@
         <v>412</v>
       </c>
       <c r="P78">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="Y78" t="s">
         <v>412</v>
@@ -6968,13 +6998,13 @@
         <v>1</v>
       </c>
       <c r="AK78" s="9">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="AL78" s="9">
         <v>0</v>
       </c>
       <c r="AM78" s="9">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="AN78" t="s">
         <v>430</v>
@@ -7006,13 +7036,13 @@
         <v>411</v>
       </c>
       <c r="K79">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O79" t="s">
         <v>412</v>
       </c>
       <c r="P79">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="Y79" t="s">
         <v>412</v>
@@ -7021,16 +7051,16 @@
         <v>413</v>
       </c>
       <c r="AJ79" s="9">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AK79" s="9">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="AL79" s="9">
         <v>0</v>
       </c>
       <c r="AM79" s="9">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="AN79" t="s">
         <v>430</v>
@@ -7062,13 +7092,13 @@
         <v>411</v>
       </c>
       <c r="K80">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O80" t="s">
         <v>412</v>
       </c>
       <c r="P80">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="Y80" t="s">
         <v>412</v>
@@ -7077,16 +7107,16 @@
         <v>413</v>
       </c>
       <c r="AJ80" s="9">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AK80" s="9">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="AL80" s="9">
         <v>0</v>
       </c>
       <c r="AM80" s="9">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="AN80" t="s">
         <v>431</v>
@@ -7118,13 +7148,13 @@
         <v>411</v>
       </c>
       <c r="K81">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O81" t="s">
         <v>412</v>
       </c>
       <c r="P81">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="Y81" t="s">
         <v>412</v>
@@ -7133,16 +7163,16 @@
         <v>413</v>
       </c>
       <c r="AJ81" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK81" s="9">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AL81" s="9">
         <v>0</v>
       </c>
       <c r="AM81" s="9">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AN81" t="s">
         <v>431</v>
@@ -7174,13 +7204,13 @@
         <v>411</v>
       </c>
       <c r="K82">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="O82" t="s">
         <v>412</v>
       </c>
       <c r="P82">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="Y82" t="s">
         <v>412</v>
@@ -7189,16 +7219,16 @@
         <v>413</v>
       </c>
       <c r="AJ82" s="9">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AK82" s="9">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="AL82" s="9">
         <v>0</v>
       </c>
       <c r="AM82" s="9">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AN82" t="s">
         <v>431</v>
@@ -7230,13 +7260,13 @@
         <v>411</v>
       </c>
       <c r="K83">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O83" t="s">
         <v>412</v>
       </c>
       <c r="P83">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="Y83" t="s">
         <v>412</v>
@@ -7245,16 +7275,16 @@
         <v>413</v>
       </c>
       <c r="AJ83" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AK83" s="9">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="AL83" s="9">
         <v>0</v>
       </c>
       <c r="AM83" s="9">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="AN83" t="s">
         <v>431</v>
@@ -7286,13 +7316,13 @@
         <v>411</v>
       </c>
       <c r="K84">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="O84" t="s">
         <v>412</v>
       </c>
       <c r="P84">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="Y84" t="s">
         <v>412</v>
@@ -7301,16 +7331,16 @@
         <v>413</v>
       </c>
       <c r="AJ84" s="9">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="AK84" s="9">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="AL84" s="9">
         <v>0</v>
       </c>
       <c r="AM84" s="9">
-        <v>75</v>
+        <v>107</v>
       </c>
       <c r="AN84" t="s">
         <v>431</v>
@@ -7342,13 +7372,13 @@
         <v>411</v>
       </c>
       <c r="K85">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="O85" t="s">
         <v>412</v>
       </c>
       <c r="P85">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="Y85" t="s">
         <v>412</v>
@@ -7357,16 +7387,16 @@
         <v>413</v>
       </c>
       <c r="AJ85" s="9">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AK85" s="9">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="AL85" s="9">
         <v>0</v>
       </c>
       <c r="AM85" s="9">
-        <v>97</v>
+        <v>58</v>
       </c>
       <c r="AN85" t="s">
         <v>431</v>
@@ -7398,13 +7428,13 @@
         <v>411</v>
       </c>
       <c r="K86">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O86" t="s">
         <v>412</v>
       </c>
       <c r="P86">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="Y86" t="s">
         <v>412</v>
@@ -7413,16 +7443,16 @@
         <v>413</v>
       </c>
       <c r="AJ86" s="9">
+        <v>3</v>
+      </c>
+      <c r="AK86" s="9">
         <v>2</v>
       </c>
-      <c r="AK86" s="9">
-        <v>30</v>
-      </c>
       <c r="AL86" s="9">
         <v>0</v>
       </c>
       <c r="AM86" s="9">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="AN86" t="s">
         <v>432</v>
@@ -7460,7 +7490,7 @@
         <v>412</v>
       </c>
       <c r="P87">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="Y87" t="s">
         <v>412</v>
@@ -7472,13 +7502,13 @@
         <v>7</v>
       </c>
       <c r="AK87" s="9">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="AL87" s="9">
         <v>0</v>
       </c>
       <c r="AM87" s="9">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="AN87" t="s">
         <v>432</v>
@@ -7510,13 +7540,13 @@
         <v>411</v>
       </c>
       <c r="K88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O88" t="s">
         <v>412</v>
       </c>
       <c r="P88">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Y88" t="s">
         <v>412</v>
@@ -7525,16 +7555,16 @@
         <v>413</v>
       </c>
       <c r="AJ88" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK88" s="9">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AL88" s="9">
         <v>0</v>
       </c>
       <c r="AM88" s="9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AN88" t="s">
         <v>432</v>
@@ -7572,7 +7602,7 @@
         <v>412</v>
       </c>
       <c r="P89">
-        <v>213</v>
+        <v>251</v>
       </c>
       <c r="Y89" t="s">
         <v>412</v>
@@ -7584,13 +7614,13 @@
         <v>38</v>
       </c>
       <c r="AK89" s="9">
-        <v>213</v>
+        <v>251</v>
       </c>
       <c r="AL89" s="9">
         <v>0</v>
       </c>
       <c r="AM89" s="9">
-        <v>251</v>
+        <v>289</v>
       </c>
       <c r="AN89" t="s">
         <v>432</v>
@@ -7628,7 +7658,7 @@
         <v>412</v>
       </c>
       <c r="P90">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="Y90" t="s">
         <v>412</v>
@@ -7640,13 +7670,13 @@
         <v>35</v>
       </c>
       <c r="AK90" s="9">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="AL90" s="9">
         <v>0</v>
       </c>
       <c r="AM90" s="9">
-        <v>199</v>
+        <v>175</v>
       </c>
       <c r="AN90" t="s">
         <v>432</v>
@@ -7684,7 +7714,7 @@
         <v>412</v>
       </c>
       <c r="P91">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="Y91" t="s">
         <v>412</v>
@@ -7696,13 +7726,13 @@
         <v>1</v>
       </c>
       <c r="AK91" s="9">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="AL91" s="9">
         <v>0</v>
       </c>
       <c r="AM91" s="9">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="AN91" t="s">
         <v>432</v>
@@ -7734,13 +7764,13 @@
         <v>411</v>
       </c>
       <c r="K92">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="O92" t="s">
         <v>412</v>
       </c>
       <c r="P92">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="Y92" t="s">
         <v>412</v>
@@ -7749,16 +7779,16 @@
         <v>413</v>
       </c>
       <c r="AJ92" s="9">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="AK92" s="9">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="AL92" s="9">
         <v>0</v>
       </c>
       <c r="AM92" s="9">
-        <v>134</v>
+        <v>167</v>
       </c>
       <c r="AN92" t="s">
         <v>433</v>
@@ -7790,13 +7820,13 @@
         <v>411</v>
       </c>
       <c r="K93">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="O93" t="s">
         <v>412</v>
       </c>
       <c r="P93">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="Y93" t="s">
         <v>412</v>
@@ -7805,16 +7835,16 @@
         <v>413</v>
       </c>
       <c r="AJ93" s="9">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AK93" s="9">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AL93" s="9">
         <v>0</v>
       </c>
       <c r="AM93" s="9">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="AN93" t="s">
         <v>433</v>
@@ -7846,7 +7876,7 @@
         <v>411</v>
       </c>
       <c r="K94">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="O94" t="s">
         <v>412</v>
@@ -7861,7 +7891,7 @@
         <v>413</v>
       </c>
       <c r="AJ94" s="9">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AK94" s="9">
         <v>22</v>
@@ -7870,7 +7900,7 @@
         <v>0</v>
       </c>
       <c r="AM94" s="9">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="AN94" t="s">
         <v>433</v>
@@ -7902,13 +7932,13 @@
         <v>411</v>
       </c>
       <c r="K95">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="O95" t="s">
         <v>412</v>
       </c>
       <c r="P95">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="Y95" t="s">
         <v>412</v>
@@ -7917,16 +7947,16 @@
         <v>413</v>
       </c>
       <c r="AJ95" s="9">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="AK95" s="9">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="AL95" s="9">
         <v>0</v>
       </c>
       <c r="AM95" s="9">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="AN95" t="s">
         <v>433</v>
@@ -7958,13 +7988,13 @@
         <v>411</v>
       </c>
       <c r="K96">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O96" t="s">
         <v>412</v>
       </c>
       <c r="P96">
-        <v>135</v>
+        <v>193</v>
       </c>
       <c r="Y96" t="s">
         <v>412</v>
@@ -7973,16 +8003,16 @@
         <v>413</v>
       </c>
       <c r="AJ96" s="9">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AK96" s="9">
-        <v>135</v>
+        <v>193</v>
       </c>
       <c r="AL96" s="9">
         <v>0</v>
       </c>
       <c r="AM96" s="9">
-        <v>179</v>
+        <v>236</v>
       </c>
       <c r="AN96" t="s">
         <v>433</v>
@@ -8014,13 +8044,13 @@
         <v>411</v>
       </c>
       <c r="K97">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="O97" t="s">
         <v>412</v>
       </c>
       <c r="P97">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="Y97" t="s">
         <v>412</v>
@@ -8029,19 +8059,3379 @@
         <v>413</v>
       </c>
       <c r="AJ97" s="9">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="AK97" s="9">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="AL97" s="9">
         <v>0</v>
       </c>
       <c r="AM97" s="9">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="AN97" t="s">
         <v>433</v>
+      </c>
+    </row>
+    <row r="98" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>407</v>
+      </c>
+      <c r="B98" t="s">
+        <v>408</v>
+      </c>
+      <c r="C98">
+        <v>17</v>
+      </c>
+      <c r="D98">
+        <v>9401</v>
+      </c>
+      <c r="E98" t="s">
+        <v>409</v>
+      </c>
+      <c r="F98">
+        <v>1</v>
+      </c>
+      <c r="G98" t="s">
+        <v>410</v>
+      </c>
+      <c r="H98" t="s">
+        <v>411</v>
+      </c>
+      <c r="K98">
+        <v>47</v>
+      </c>
+      <c r="O98" t="s">
+        <v>412</v>
+      </c>
+      <c r="P98">
+        <v>141</v>
+      </c>
+      <c r="Y98" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI98" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ98" s="9">
+        <v>47</v>
+      </c>
+      <c r="AK98" s="9">
+        <v>141</v>
+      </c>
+      <c r="AL98" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM98" s="9">
+        <v>188</v>
+      </c>
+      <c r="AN98" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="99" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>407</v>
+      </c>
+      <c r="B99" t="s">
+        <v>408</v>
+      </c>
+      <c r="C99">
+        <v>17</v>
+      </c>
+      <c r="D99">
+        <v>4423</v>
+      </c>
+      <c r="E99" t="s">
+        <v>409</v>
+      </c>
+      <c r="F99">
+        <v>2</v>
+      </c>
+      <c r="G99" t="s">
+        <v>410</v>
+      </c>
+      <c r="H99" t="s">
+        <v>411</v>
+      </c>
+      <c r="K99">
+        <v>3</v>
+      </c>
+      <c r="O99" t="s">
+        <v>412</v>
+      </c>
+      <c r="P99">
+        <v>22</v>
+      </c>
+      <c r="Y99" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI99" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ99" s="9">
+        <v>3</v>
+      </c>
+      <c r="AK99" s="9">
+        <v>22</v>
+      </c>
+      <c r="AL99" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM99" s="9">
+        <v>25</v>
+      </c>
+      <c r="AN99" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="100" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>407</v>
+      </c>
+      <c r="B100" t="s">
+        <v>408</v>
+      </c>
+      <c r="C100">
+        <v>17</v>
+      </c>
+      <c r="D100">
+        <v>2338</v>
+      </c>
+      <c r="E100" t="s">
+        <v>409</v>
+      </c>
+      <c r="F100">
+        <v>3</v>
+      </c>
+      <c r="G100" t="s">
+        <v>410</v>
+      </c>
+      <c r="H100" t="s">
+        <v>411</v>
+      </c>
+      <c r="K100">
+        <v>41</v>
+      </c>
+      <c r="O100" t="s">
+        <v>412</v>
+      </c>
+      <c r="P100">
+        <v>126</v>
+      </c>
+      <c r="Y100" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI100" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ100" s="9">
+        <v>41</v>
+      </c>
+      <c r="AK100" s="9">
+        <v>126</v>
+      </c>
+      <c r="AL100" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM100" s="9">
+        <v>167</v>
+      </c>
+      <c r="AN100" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="101" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>407</v>
+      </c>
+      <c r="B101" t="s">
+        <v>408</v>
+      </c>
+      <c r="C101">
+        <v>17</v>
+      </c>
+      <c r="D101">
+        <v>1706</v>
+      </c>
+      <c r="E101" t="s">
+        <v>415</v>
+      </c>
+      <c r="F101">
+        <v>1</v>
+      </c>
+      <c r="G101" t="s">
+        <v>410</v>
+      </c>
+      <c r="H101" t="s">
+        <v>411</v>
+      </c>
+      <c r="K101">
+        <v>56</v>
+      </c>
+      <c r="O101" t="s">
+        <v>412</v>
+      </c>
+      <c r="P101">
+        <v>254</v>
+      </c>
+      <c r="Y101" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI101" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ101" s="9">
+        <v>56</v>
+      </c>
+      <c r="AK101" s="9">
+        <v>254</v>
+      </c>
+      <c r="AL101" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM101" s="9">
+        <v>310</v>
+      </c>
+      <c r="AN101" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="102" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>407</v>
+      </c>
+      <c r="B102" t="s">
+        <v>408</v>
+      </c>
+      <c r="C102">
+        <v>17</v>
+      </c>
+      <c r="D102">
+        <v>1792</v>
+      </c>
+      <c r="E102" t="s">
+        <v>415</v>
+      </c>
+      <c r="F102">
+        <v>2</v>
+      </c>
+      <c r="G102" t="s">
+        <v>410</v>
+      </c>
+      <c r="H102" t="s">
+        <v>411</v>
+      </c>
+      <c r="K102">
+        <v>32</v>
+      </c>
+      <c r="O102" t="s">
+        <v>412</v>
+      </c>
+      <c r="P102">
+        <v>59</v>
+      </c>
+      <c r="Y102" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI102" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ102" s="9">
+        <v>32</v>
+      </c>
+      <c r="AK102" s="9">
+        <v>59</v>
+      </c>
+      <c r="AL102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM102" s="9">
+        <v>91</v>
+      </c>
+      <c r="AN102" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="103" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>407</v>
+      </c>
+      <c r="B103" t="s">
+        <v>408</v>
+      </c>
+      <c r="C103">
+        <v>17</v>
+      </c>
+      <c r="D103">
+        <v>7117</v>
+      </c>
+      <c r="E103" t="s">
+        <v>415</v>
+      </c>
+      <c r="F103">
+        <v>3</v>
+      </c>
+      <c r="G103" t="s">
+        <v>410</v>
+      </c>
+      <c r="H103" t="s">
+        <v>411</v>
+      </c>
+      <c r="K103">
+        <v>33</v>
+      </c>
+      <c r="O103" t="s">
+        <v>412</v>
+      </c>
+      <c r="P103">
+        <v>75</v>
+      </c>
+      <c r="Y103" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI103" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ103" s="9">
+        <v>33</v>
+      </c>
+      <c r="AK103" s="9">
+        <v>75</v>
+      </c>
+      <c r="AL103" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM103" s="9">
+        <v>108</v>
+      </c>
+      <c r="AN103" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="104" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>407</v>
+      </c>
+      <c r="B104" t="s">
+        <v>408</v>
+      </c>
+      <c r="C104">
+        <v>18</v>
+      </c>
+      <c r="D104">
+        <v>5934</v>
+      </c>
+      <c r="E104" t="s">
+        <v>409</v>
+      </c>
+      <c r="F104">
+        <v>1</v>
+      </c>
+      <c r="G104" t="s">
+        <v>410</v>
+      </c>
+      <c r="H104" t="s">
+        <v>411</v>
+      </c>
+      <c r="K104">
+        <v>25</v>
+      </c>
+      <c r="O104" t="s">
+        <v>412</v>
+      </c>
+      <c r="P104">
+        <v>46</v>
+      </c>
+      <c r="Y104" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI104" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ104" s="9">
+        <v>25</v>
+      </c>
+      <c r="AK104" s="9">
+        <v>46</v>
+      </c>
+      <c r="AL104" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM104" s="9">
+        <v>71</v>
+      </c>
+      <c r="AN104" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="105" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>407</v>
+      </c>
+      <c r="B105" t="s">
+        <v>408</v>
+      </c>
+      <c r="C105">
+        <v>18</v>
+      </c>
+      <c r="D105">
+        <v>4143</v>
+      </c>
+      <c r="E105" t="s">
+        <v>409</v>
+      </c>
+      <c r="F105">
+        <v>2</v>
+      </c>
+      <c r="G105" t="s">
+        <v>410</v>
+      </c>
+      <c r="H105" t="s">
+        <v>411</v>
+      </c>
+      <c r="K105">
+        <v>3</v>
+      </c>
+      <c r="O105" t="s">
+        <v>412</v>
+      </c>
+      <c r="P105">
+        <v>45</v>
+      </c>
+      <c r="Y105" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI105" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ105" s="9">
+        <v>3</v>
+      </c>
+      <c r="AK105" s="9">
+        <v>45</v>
+      </c>
+      <c r="AL105" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM105" s="9">
+        <v>48</v>
+      </c>
+      <c r="AN105" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="106" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>407</v>
+      </c>
+      <c r="B106" t="s">
+        <v>408</v>
+      </c>
+      <c r="C106">
+        <v>18</v>
+      </c>
+      <c r="D106">
+        <v>111</v>
+      </c>
+      <c r="E106" t="s">
+        <v>409</v>
+      </c>
+      <c r="F106">
+        <v>3</v>
+      </c>
+      <c r="G106" t="s">
+        <v>410</v>
+      </c>
+      <c r="H106" t="s">
+        <v>411</v>
+      </c>
+      <c r="K106">
+        <v>26</v>
+      </c>
+      <c r="O106" t="s">
+        <v>412</v>
+      </c>
+      <c r="P106">
+        <v>38</v>
+      </c>
+      <c r="Y106" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI106" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ106" s="9">
+        <v>26</v>
+      </c>
+      <c r="AK106" s="9">
+        <v>38</v>
+      </c>
+      <c r="AL106" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM106" s="9">
+        <v>64</v>
+      </c>
+      <c r="AN106" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="107" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>407</v>
+      </c>
+      <c r="B107" t="s">
+        <v>408</v>
+      </c>
+      <c r="C107">
+        <v>18</v>
+      </c>
+      <c r="D107" t="s">
+        <v>419</v>
+      </c>
+      <c r="E107" t="s">
+        <v>415</v>
+      </c>
+      <c r="F107">
+        <v>1</v>
+      </c>
+      <c r="G107" t="s">
+        <v>410</v>
+      </c>
+      <c r="H107" t="s">
+        <v>411</v>
+      </c>
+      <c r="K107">
+        <v>40</v>
+      </c>
+      <c r="O107" t="s">
+        <v>412</v>
+      </c>
+      <c r="P107">
+        <v>133</v>
+      </c>
+      <c r="Y107" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI107" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ107" s="9">
+        <v>40</v>
+      </c>
+      <c r="AK107" s="9">
+        <v>133</v>
+      </c>
+      <c r="AL107" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM107" s="9">
+        <v>173</v>
+      </c>
+      <c r="AN107" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="108" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>407</v>
+      </c>
+      <c r="B108" t="s">
+        <v>408</v>
+      </c>
+      <c r="C108">
+        <v>18</v>
+      </c>
+      <c r="D108">
+        <v>1781</v>
+      </c>
+      <c r="E108" t="s">
+        <v>415</v>
+      </c>
+      <c r="F108">
+        <v>2</v>
+      </c>
+      <c r="G108" t="s">
+        <v>410</v>
+      </c>
+      <c r="H108" t="s">
+        <v>411</v>
+      </c>
+      <c r="K108">
+        <v>9</v>
+      </c>
+      <c r="O108" t="s">
+        <v>412</v>
+      </c>
+      <c r="P108">
+        <v>4</v>
+      </c>
+      <c r="Y108" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI108" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ108" s="9">
+        <v>9</v>
+      </c>
+      <c r="AK108" s="9">
+        <v>4</v>
+      </c>
+      <c r="AL108" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM108" s="9">
+        <v>13</v>
+      </c>
+      <c r="AN108" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="109" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>407</v>
+      </c>
+      <c r="B109" t="s">
+        <v>408</v>
+      </c>
+      <c r="C109">
+        <v>18</v>
+      </c>
+      <c r="D109">
+        <v>1756</v>
+      </c>
+      <c r="E109" t="s">
+        <v>415</v>
+      </c>
+      <c r="F109">
+        <v>3</v>
+      </c>
+      <c r="G109" t="s">
+        <v>410</v>
+      </c>
+      <c r="H109" t="s">
+        <v>411</v>
+      </c>
+      <c r="K109">
+        <v>43</v>
+      </c>
+      <c r="O109" t="s">
+        <v>412</v>
+      </c>
+      <c r="P109">
+        <v>156</v>
+      </c>
+      <c r="Y109" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI109" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ109" s="9">
+        <v>43</v>
+      </c>
+      <c r="AK109" s="9">
+        <v>156</v>
+      </c>
+      <c r="AL109" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM109" s="9">
+        <v>199</v>
+      </c>
+      <c r="AN109" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="110" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>407</v>
+      </c>
+      <c r="B110" t="s">
+        <v>408</v>
+      </c>
+      <c r="C110">
+        <v>20</v>
+      </c>
+      <c r="D110">
+        <v>3197</v>
+      </c>
+      <c r="E110" t="s">
+        <v>409</v>
+      </c>
+      <c r="F110">
+        <v>1</v>
+      </c>
+      <c r="G110" t="s">
+        <v>410</v>
+      </c>
+      <c r="H110" t="s">
+        <v>411</v>
+      </c>
+      <c r="K110">
+        <v>7</v>
+      </c>
+      <c r="O110" t="s">
+        <v>412</v>
+      </c>
+      <c r="P110">
+        <v>28</v>
+      </c>
+      <c r="Y110" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI110" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ110" s="9">
+        <v>7</v>
+      </c>
+      <c r="AK110" s="9">
+        <v>28</v>
+      </c>
+      <c r="AL110" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM110" s="9">
+        <v>35</v>
+      </c>
+      <c r="AN110" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="111" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>407</v>
+      </c>
+      <c r="B111" t="s">
+        <v>408</v>
+      </c>
+      <c r="C111">
+        <v>20</v>
+      </c>
+      <c r="D111">
+        <v>2290</v>
+      </c>
+      <c r="E111" t="s">
+        <v>409</v>
+      </c>
+      <c r="F111">
+        <v>2</v>
+      </c>
+      <c r="G111" t="s">
+        <v>410</v>
+      </c>
+      <c r="H111" t="s">
+        <v>411</v>
+      </c>
+      <c r="K111">
+        <v>7</v>
+      </c>
+      <c r="O111" t="s">
+        <v>412</v>
+      </c>
+      <c r="P111">
+        <v>6</v>
+      </c>
+      <c r="Y111" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI111" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ111" s="9">
+        <v>7</v>
+      </c>
+      <c r="AK111" s="9">
+        <v>6</v>
+      </c>
+      <c r="AL111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM111" s="9">
+        <v>13</v>
+      </c>
+      <c r="AN111" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="112" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>407</v>
+      </c>
+      <c r="B112" t="s">
+        <v>408</v>
+      </c>
+      <c r="C112">
+        <v>20</v>
+      </c>
+      <c r="D112">
+        <v>1736</v>
+      </c>
+      <c r="E112" t="s">
+        <v>409</v>
+      </c>
+      <c r="F112">
+        <v>3</v>
+      </c>
+      <c r="G112" t="s">
+        <v>410</v>
+      </c>
+      <c r="H112" t="s">
+        <v>411</v>
+      </c>
+      <c r="K112">
+        <v>0</v>
+      </c>
+      <c r="O112" t="s">
+        <v>412</v>
+      </c>
+      <c r="P112">
+        <v>0</v>
+      </c>
+      <c r="Y112" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI112" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ112" s="9">
+        <v>0</v>
+      </c>
+      <c r="AK112" s="9">
+        <v>0</v>
+      </c>
+      <c r="AL112" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM112" s="9">
+        <v>0</v>
+      </c>
+      <c r="AN112" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="113" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>407</v>
+      </c>
+      <c r="B113" t="s">
+        <v>408</v>
+      </c>
+      <c r="C113">
+        <v>20</v>
+      </c>
+      <c r="D113">
+        <v>9401</v>
+      </c>
+      <c r="E113" t="s">
+        <v>415</v>
+      </c>
+      <c r="F113">
+        <v>1</v>
+      </c>
+      <c r="G113" t="s">
+        <v>410</v>
+      </c>
+      <c r="H113" t="s">
+        <v>411</v>
+      </c>
+      <c r="K113">
+        <v>47</v>
+      </c>
+      <c r="O113" t="s">
+        <v>412</v>
+      </c>
+      <c r="P113">
+        <v>161</v>
+      </c>
+      <c r="Y113" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI113" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ113" s="9">
+        <v>47</v>
+      </c>
+      <c r="AK113" s="9">
+        <v>161</v>
+      </c>
+      <c r="AL113" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM113" s="9">
+        <v>208</v>
+      </c>
+      <c r="AN113" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="114" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>407</v>
+      </c>
+      <c r="B114" t="s">
+        <v>408</v>
+      </c>
+      <c r="C114">
+        <v>20</v>
+      </c>
+      <c r="D114">
+        <v>2481</v>
+      </c>
+      <c r="E114" t="s">
+        <v>415</v>
+      </c>
+      <c r="F114">
+        <v>2</v>
+      </c>
+      <c r="G114" t="s">
+        <v>410</v>
+      </c>
+      <c r="H114" t="s">
+        <v>411</v>
+      </c>
+      <c r="K114">
+        <v>54</v>
+      </c>
+      <c r="O114" t="s">
+        <v>412</v>
+      </c>
+      <c r="P114">
+        <v>251</v>
+      </c>
+      <c r="Y114" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI114" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ114" s="9">
+        <v>54</v>
+      </c>
+      <c r="AK114" s="9">
+        <v>251</v>
+      </c>
+      <c r="AL114" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM114" s="9">
+        <v>305</v>
+      </c>
+      <c r="AN114" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="115" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>407</v>
+      </c>
+      <c r="B115" t="s">
+        <v>408</v>
+      </c>
+      <c r="C115">
+        <v>20</v>
+      </c>
+      <c r="D115">
+        <v>3397</v>
+      </c>
+      <c r="E115" t="s">
+        <v>415</v>
+      </c>
+      <c r="F115">
+        <v>3</v>
+      </c>
+      <c r="G115" t="s">
+        <v>410</v>
+      </c>
+      <c r="H115" t="s">
+        <v>411</v>
+      </c>
+      <c r="K115">
+        <v>1</v>
+      </c>
+      <c r="O115" t="s">
+        <v>412</v>
+      </c>
+      <c r="P115">
+        <v>21</v>
+      </c>
+      <c r="Y115" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI115" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ115" s="9">
+        <v>1</v>
+      </c>
+      <c r="AK115" s="9">
+        <v>21</v>
+      </c>
+      <c r="AL115" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM115" s="9">
+        <v>22</v>
+      </c>
+      <c r="AN115" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="116" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>407</v>
+      </c>
+      <c r="B116" t="s">
+        <v>408</v>
+      </c>
+      <c r="C116">
+        <v>21</v>
+      </c>
+      <c r="D116">
+        <v>112</v>
+      </c>
+      <c r="E116" t="s">
+        <v>409</v>
+      </c>
+      <c r="F116">
+        <v>1</v>
+      </c>
+      <c r="G116" t="s">
+        <v>410</v>
+      </c>
+      <c r="H116" t="s">
+        <v>411</v>
+      </c>
+      <c r="K116">
+        <v>46</v>
+      </c>
+      <c r="O116" t="s">
+        <v>412</v>
+      </c>
+      <c r="P116">
+        <v>122</v>
+      </c>
+      <c r="Y116" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI116" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ116" s="9">
+        <v>46</v>
+      </c>
+      <c r="AK116" s="9">
+        <v>122</v>
+      </c>
+      <c r="AL116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM116" s="9">
+        <v>168</v>
+      </c>
+      <c r="AN116" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="117" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>407</v>
+      </c>
+      <c r="B117" t="s">
+        <v>408</v>
+      </c>
+      <c r="C117">
+        <v>21</v>
+      </c>
+      <c r="D117" t="s">
+        <v>419</v>
+      </c>
+      <c r="E117" t="s">
+        <v>409</v>
+      </c>
+      <c r="F117">
+        <v>2</v>
+      </c>
+      <c r="G117" t="s">
+        <v>410</v>
+      </c>
+      <c r="H117" t="s">
+        <v>411</v>
+      </c>
+      <c r="K117">
+        <v>48</v>
+      </c>
+      <c r="O117" t="s">
+        <v>412</v>
+      </c>
+      <c r="P117">
+        <v>143</v>
+      </c>
+      <c r="Y117" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI117" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ117" s="9">
+        <v>48</v>
+      </c>
+      <c r="AK117" s="9">
+        <v>143</v>
+      </c>
+      <c r="AL117" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM117" s="9">
+        <v>191</v>
+      </c>
+      <c r="AN117" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="118" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>407</v>
+      </c>
+      <c r="B118" t="s">
+        <v>408</v>
+      </c>
+      <c r="C118">
+        <v>21</v>
+      </c>
+      <c r="D118">
+        <v>1625</v>
+      </c>
+      <c r="E118" t="s">
+        <v>409</v>
+      </c>
+      <c r="F118">
+        <v>3</v>
+      </c>
+      <c r="G118" t="s">
+        <v>410</v>
+      </c>
+      <c r="H118" t="s">
+        <v>411</v>
+      </c>
+      <c r="K118">
+        <v>5</v>
+      </c>
+      <c r="O118" t="s">
+        <v>412</v>
+      </c>
+      <c r="P118">
+        <v>88</v>
+      </c>
+      <c r="Y118" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI118" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ118" s="9">
+        <v>5</v>
+      </c>
+      <c r="AK118" s="9">
+        <v>88</v>
+      </c>
+      <c r="AL118" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM118" s="9">
+        <v>93</v>
+      </c>
+      <c r="AN118" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="119" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>407</v>
+      </c>
+      <c r="B119" t="s">
+        <v>408</v>
+      </c>
+      <c r="C119">
+        <v>21</v>
+      </c>
+      <c r="D119">
+        <v>7457</v>
+      </c>
+      <c r="E119" t="s">
+        <v>415</v>
+      </c>
+      <c r="F119">
+        <v>1</v>
+      </c>
+      <c r="G119" t="s">
+        <v>410</v>
+      </c>
+      <c r="H119" t="s">
+        <v>411</v>
+      </c>
+      <c r="K119">
+        <v>39</v>
+      </c>
+      <c r="O119" t="s">
+        <v>412</v>
+      </c>
+      <c r="P119">
+        <v>196</v>
+      </c>
+      <c r="Y119" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI119" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ119" s="9">
+        <v>39</v>
+      </c>
+      <c r="AK119" s="9">
+        <v>196</v>
+      </c>
+      <c r="AL119" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM119" s="9">
+        <v>235</v>
+      </c>
+      <c r="AN119" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="120" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>407</v>
+      </c>
+      <c r="B120" t="s">
+        <v>408</v>
+      </c>
+      <c r="C120">
+        <v>21</v>
+      </c>
+      <c r="D120">
+        <v>648</v>
+      </c>
+      <c r="E120" t="s">
+        <v>415</v>
+      </c>
+      <c r="F120">
+        <v>2</v>
+      </c>
+      <c r="G120" t="s">
+        <v>410</v>
+      </c>
+      <c r="H120" t="s">
+        <v>411</v>
+      </c>
+      <c r="K120">
+        <v>16</v>
+      </c>
+      <c r="O120" t="s">
+        <v>412</v>
+      </c>
+      <c r="P120">
+        <v>112</v>
+      </c>
+      <c r="Y120" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI120" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ120" s="9">
+        <v>16</v>
+      </c>
+      <c r="AK120" s="9">
+        <v>112</v>
+      </c>
+      <c r="AL120" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM120" s="9">
+        <v>128</v>
+      </c>
+      <c r="AN120" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="121" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>407</v>
+      </c>
+      <c r="B121" t="s">
+        <v>408</v>
+      </c>
+      <c r="C121">
+        <v>21</v>
+      </c>
+      <c r="D121">
+        <v>4423</v>
+      </c>
+      <c r="E121" t="s">
+        <v>415</v>
+      </c>
+      <c r="F121">
+        <v>3</v>
+      </c>
+      <c r="G121" t="s">
+        <v>410</v>
+      </c>
+      <c r="H121" t="s">
+        <v>411</v>
+      </c>
+      <c r="K121">
+        <v>3</v>
+      </c>
+      <c r="O121" t="s">
+        <v>412</v>
+      </c>
+      <c r="P121">
+        <v>25</v>
+      </c>
+      <c r="Y121" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI121" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ121" s="9">
+        <v>3</v>
+      </c>
+      <c r="AK121" s="9">
+        <v>25</v>
+      </c>
+      <c r="AL121" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM121" s="9">
+        <v>28</v>
+      </c>
+      <c r="AN121" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="122" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>407</v>
+      </c>
+      <c r="B122" t="s">
+        <v>408</v>
+      </c>
+      <c r="C122">
+        <v>22</v>
+      </c>
+      <c r="D122">
+        <v>930</v>
+      </c>
+      <c r="E122" t="s">
+        <v>409</v>
+      </c>
+      <c r="F122">
+        <v>1</v>
+      </c>
+      <c r="G122" t="s">
+        <v>410</v>
+      </c>
+      <c r="H122" t="s">
+        <v>411</v>
+      </c>
+      <c r="K122">
+        <v>44</v>
+      </c>
+      <c r="O122" t="s">
+        <v>412</v>
+      </c>
+      <c r="P122">
+        <v>118</v>
+      </c>
+      <c r="Y122" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI122" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ122" s="9">
+        <v>44</v>
+      </c>
+      <c r="AK122" s="9">
+        <v>118</v>
+      </c>
+      <c r="AL122" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM122" s="9">
+        <v>162</v>
+      </c>
+      <c r="AN122" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="123" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>407</v>
+      </c>
+      <c r="B123" t="s">
+        <v>408</v>
+      </c>
+      <c r="C123">
+        <v>22</v>
+      </c>
+      <c r="D123">
+        <v>9082</v>
+      </c>
+      <c r="E123" t="s">
+        <v>409</v>
+      </c>
+      <c r="F123">
+        <v>2</v>
+      </c>
+      <c r="G123" t="s">
+        <v>410</v>
+      </c>
+      <c r="H123" t="s">
+        <v>411</v>
+      </c>
+      <c r="K123">
+        <v>4</v>
+      </c>
+      <c r="O123" t="s">
+        <v>412</v>
+      </c>
+      <c r="P123">
+        <v>18</v>
+      </c>
+      <c r="Y123" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI123" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ123" s="9">
+        <v>4</v>
+      </c>
+      <c r="AK123" s="9">
+        <v>18</v>
+      </c>
+      <c r="AL123" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM123" s="9">
+        <v>22</v>
+      </c>
+      <c r="AN123" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="124" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>407</v>
+      </c>
+      <c r="B124" t="s">
+        <v>408</v>
+      </c>
+      <c r="C124">
+        <v>22</v>
+      </c>
+      <c r="D124">
+        <v>4143</v>
+      </c>
+      <c r="E124" t="s">
+        <v>409</v>
+      </c>
+      <c r="F124">
+        <v>3</v>
+      </c>
+      <c r="G124" t="s">
+        <v>410</v>
+      </c>
+      <c r="H124" t="s">
+        <v>411</v>
+      </c>
+      <c r="K124">
+        <v>3</v>
+      </c>
+      <c r="O124" t="s">
+        <v>412</v>
+      </c>
+      <c r="P124">
+        <v>45</v>
+      </c>
+      <c r="Y124" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI124" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ124" s="9">
+        <v>3</v>
+      </c>
+      <c r="AK124" s="9">
+        <v>45</v>
+      </c>
+      <c r="AL124" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM124" s="9">
+        <v>48</v>
+      </c>
+      <c r="AN124" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="125" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>407</v>
+      </c>
+      <c r="B125" t="s">
+        <v>408</v>
+      </c>
+      <c r="C125">
+        <v>22</v>
+      </c>
+      <c r="D125">
+        <v>5125</v>
+      </c>
+      <c r="E125" t="s">
+        <v>415</v>
+      </c>
+      <c r="F125">
+        <v>1</v>
+      </c>
+      <c r="G125" t="s">
+        <v>410</v>
+      </c>
+      <c r="H125" t="s">
+        <v>411</v>
+      </c>
+      <c r="K125">
+        <v>1</v>
+      </c>
+      <c r="O125" t="s">
+        <v>412</v>
+      </c>
+      <c r="P125">
+        <v>41</v>
+      </c>
+      <c r="Y125" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI125" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ125" s="9">
+        <v>1</v>
+      </c>
+      <c r="AK125" s="9">
+        <v>41</v>
+      </c>
+      <c r="AL125" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM125" s="9">
+        <v>42</v>
+      </c>
+      <c r="AN125" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="126" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>407</v>
+      </c>
+      <c r="B126" t="s">
+        <v>408</v>
+      </c>
+      <c r="C126">
+        <v>22</v>
+      </c>
+      <c r="D126">
+        <v>2338</v>
+      </c>
+      <c r="E126" t="s">
+        <v>415</v>
+      </c>
+      <c r="F126">
+        <v>2</v>
+      </c>
+      <c r="G126" t="s">
+        <v>410</v>
+      </c>
+      <c r="H126" t="s">
+        <v>411</v>
+      </c>
+      <c r="K126">
+        <v>39</v>
+      </c>
+      <c r="O126" t="s">
+        <v>412</v>
+      </c>
+      <c r="P126">
+        <v>141</v>
+      </c>
+      <c r="Y126" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI126" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ126" s="9">
+        <v>39</v>
+      </c>
+      <c r="AK126" s="9">
+        <v>141</v>
+      </c>
+      <c r="AL126" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM126" s="9">
+        <v>180</v>
+      </c>
+      <c r="AN126" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="127" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>407</v>
+      </c>
+      <c r="B127" t="s">
+        <v>408</v>
+      </c>
+      <c r="C127">
+        <v>22</v>
+      </c>
+      <c r="D127">
+        <v>4655</v>
+      </c>
+      <c r="E127" t="s">
+        <v>415</v>
+      </c>
+      <c r="F127">
+        <v>3</v>
+      </c>
+      <c r="G127" t="s">
+        <v>410</v>
+      </c>
+      <c r="H127" t="s">
+        <v>411</v>
+      </c>
+      <c r="K127">
+        <v>27</v>
+      </c>
+      <c r="O127" t="s">
+        <v>412</v>
+      </c>
+      <c r="P127">
+        <v>104</v>
+      </c>
+      <c r="Y127" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI127" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ127" s="9">
+        <v>27</v>
+      </c>
+      <c r="AK127" s="9">
+        <v>104</v>
+      </c>
+      <c r="AL127" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM127" s="9">
+        <v>131</v>
+      </c>
+      <c r="AN127" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="128" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>407</v>
+      </c>
+      <c r="B128" t="s">
+        <v>408</v>
+      </c>
+      <c r="C128">
+        <v>23</v>
+      </c>
+      <c r="D128">
+        <v>4096</v>
+      </c>
+      <c r="E128" t="s">
+        <v>409</v>
+      </c>
+      <c r="F128">
+        <v>1</v>
+      </c>
+      <c r="G128" t="s">
+        <v>410</v>
+      </c>
+      <c r="H128" t="s">
+        <v>411</v>
+      </c>
+      <c r="K128">
+        <v>12</v>
+      </c>
+      <c r="O128" t="s">
+        <v>412</v>
+      </c>
+      <c r="P128">
+        <v>142</v>
+      </c>
+      <c r="Y128" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI128" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ128" s="9">
+        <v>12</v>
+      </c>
+      <c r="AK128" s="9">
+        <v>142</v>
+      </c>
+      <c r="AL128" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM128" s="9">
+        <v>154</v>
+      </c>
+      <c r="AN128" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="129" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>407</v>
+      </c>
+      <c r="B129" t="s">
+        <v>408</v>
+      </c>
+      <c r="C129">
+        <v>23</v>
+      </c>
+      <c r="D129">
+        <v>11173</v>
+      </c>
+      <c r="E129" t="s">
+        <v>409</v>
+      </c>
+      <c r="F129">
+        <v>2</v>
+      </c>
+      <c r="G129" t="s">
+        <v>410</v>
+      </c>
+      <c r="H129" t="s">
+        <v>411</v>
+      </c>
+      <c r="K129">
+        <v>29</v>
+      </c>
+      <c r="O129" t="s">
+        <v>412</v>
+      </c>
+      <c r="P129">
+        <v>54</v>
+      </c>
+      <c r="Y129" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI129" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ129" s="9">
+        <v>29</v>
+      </c>
+      <c r="AK129" s="9">
+        <v>54</v>
+      </c>
+      <c r="AL129" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM129" s="9">
+        <v>83</v>
+      </c>
+      <c r="AN129" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="130" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>407</v>
+      </c>
+      <c r="B130" t="s">
+        <v>408</v>
+      </c>
+      <c r="C130">
+        <v>23</v>
+      </c>
+      <c r="D130">
+        <v>5934</v>
+      </c>
+      <c r="E130" t="s">
+        <v>409</v>
+      </c>
+      <c r="F130">
+        <v>3</v>
+      </c>
+      <c r="G130" t="s">
+        <v>410</v>
+      </c>
+      <c r="H130" t="s">
+        <v>411</v>
+      </c>
+      <c r="K130">
+        <v>31</v>
+      </c>
+      <c r="O130" t="s">
+        <v>412</v>
+      </c>
+      <c r="P130">
+        <v>51</v>
+      </c>
+      <c r="Y130" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI130" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ130" s="9">
+        <v>31</v>
+      </c>
+      <c r="AK130" s="9">
+        <v>51</v>
+      </c>
+      <c r="AL130" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM130" s="9">
+        <v>82</v>
+      </c>
+      <c r="AN130" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="131" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>407</v>
+      </c>
+      <c r="B131" t="s">
+        <v>408</v>
+      </c>
+      <c r="C131">
+        <v>23</v>
+      </c>
+      <c r="D131">
+        <v>2040</v>
+      </c>
+      <c r="E131" t="s">
+        <v>415</v>
+      </c>
+      <c r="F131">
+        <v>1</v>
+      </c>
+      <c r="G131" t="s">
+        <v>410</v>
+      </c>
+      <c r="H131" t="s">
+        <v>411</v>
+      </c>
+      <c r="K131">
+        <v>40</v>
+      </c>
+      <c r="O131" t="s">
+        <v>412</v>
+      </c>
+      <c r="P131">
+        <v>82</v>
+      </c>
+      <c r="Y131" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI131" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ131" s="9">
+        <v>40</v>
+      </c>
+      <c r="AK131" s="9">
+        <v>82</v>
+      </c>
+      <c r="AL131" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM131" s="9">
+        <v>122</v>
+      </c>
+      <c r="AN131" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="132" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>407</v>
+      </c>
+      <c r="B132" t="s">
+        <v>408</v>
+      </c>
+      <c r="C132">
+        <v>23</v>
+      </c>
+      <c r="D132">
+        <v>1792</v>
+      </c>
+      <c r="E132" t="s">
+        <v>415</v>
+      </c>
+      <c r="F132">
+        <v>2</v>
+      </c>
+      <c r="G132" t="s">
+        <v>410</v>
+      </c>
+      <c r="H132" t="s">
+        <v>411</v>
+      </c>
+      <c r="K132">
+        <v>34</v>
+      </c>
+      <c r="O132" t="s">
+        <v>412</v>
+      </c>
+      <c r="P132">
+        <v>45</v>
+      </c>
+      <c r="Y132" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI132" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ132" s="9">
+        <v>34</v>
+      </c>
+      <c r="AK132" s="9">
+        <v>45</v>
+      </c>
+      <c r="AL132" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM132" s="9">
+        <v>79</v>
+      </c>
+      <c r="AN132" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="133" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>407</v>
+      </c>
+      <c r="B133" t="s">
+        <v>408</v>
+      </c>
+      <c r="C133">
+        <v>23</v>
+      </c>
+      <c r="D133">
+        <v>5822</v>
+      </c>
+      <c r="E133" t="s">
+        <v>415</v>
+      </c>
+      <c r="F133">
+        <v>3</v>
+      </c>
+      <c r="G133" t="s">
+        <v>410</v>
+      </c>
+      <c r="H133" t="s">
+        <v>411</v>
+      </c>
+      <c r="K133">
+        <v>7</v>
+      </c>
+      <c r="O133" t="s">
+        <v>412</v>
+      </c>
+      <c r="P133">
+        <v>24</v>
+      </c>
+      <c r="Y133" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI133" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ133" s="9">
+        <v>7</v>
+      </c>
+      <c r="AK133" s="9">
+        <v>24</v>
+      </c>
+      <c r="AL133" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM133" s="9">
+        <v>31</v>
+      </c>
+      <c r="AN133" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="134" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>407</v>
+      </c>
+      <c r="B134" t="s">
+        <v>408</v>
+      </c>
+      <c r="C134">
+        <v>24</v>
+      </c>
+      <c r="D134">
+        <v>7117</v>
+      </c>
+      <c r="E134" t="s">
+        <v>409</v>
+      </c>
+      <c r="F134">
+        <v>1</v>
+      </c>
+      <c r="G134" t="s">
+        <v>410</v>
+      </c>
+      <c r="H134" t="s">
+        <v>411</v>
+      </c>
+      <c r="K134">
+        <v>36</v>
+      </c>
+      <c r="O134" t="s">
+        <v>412</v>
+      </c>
+      <c r="P134">
+        <v>66</v>
+      </c>
+      <c r="Y134" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI134" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ134" s="9">
+        <v>36</v>
+      </c>
+      <c r="AK134" s="9">
+        <v>66</v>
+      </c>
+      <c r="AL134" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM134" s="9">
+        <v>102</v>
+      </c>
+      <c r="AN134" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="135" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>407</v>
+      </c>
+      <c r="B135" t="s">
+        <v>408</v>
+      </c>
+      <c r="C135">
+        <v>24</v>
+      </c>
+      <c r="D135" t="s">
+        <v>419</v>
+      </c>
+      <c r="E135" t="s">
+        <v>409</v>
+      </c>
+      <c r="F135">
+        <v>2</v>
+      </c>
+      <c r="G135" t="s">
+        <v>410</v>
+      </c>
+      <c r="H135" t="s">
+        <v>411</v>
+      </c>
+      <c r="K135">
+        <v>37</v>
+      </c>
+      <c r="O135" t="s">
+        <v>412</v>
+      </c>
+      <c r="P135">
+        <v>115</v>
+      </c>
+      <c r="Y135" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI135" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ135" s="9">
+        <v>37</v>
+      </c>
+      <c r="AK135" s="9">
+        <v>115</v>
+      </c>
+      <c r="AL135" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM135" s="9">
+        <v>152</v>
+      </c>
+      <c r="AN135" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="136" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>407</v>
+      </c>
+      <c r="B136" t="s">
+        <v>408</v>
+      </c>
+      <c r="C136">
+        <v>24</v>
+      </c>
+      <c r="D136">
+        <v>930</v>
+      </c>
+      <c r="E136" t="s">
+        <v>409</v>
+      </c>
+      <c r="F136">
+        <v>3</v>
+      </c>
+      <c r="G136" t="s">
+        <v>410</v>
+      </c>
+      <c r="H136" t="s">
+        <v>411</v>
+      </c>
+      <c r="K136">
+        <v>45</v>
+      </c>
+      <c r="O136" t="s">
+        <v>412</v>
+      </c>
+      <c r="P136">
+        <v>124</v>
+      </c>
+      <c r="Y136" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI136" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ136" s="9">
+        <v>45</v>
+      </c>
+      <c r="AK136" s="9">
+        <v>124</v>
+      </c>
+      <c r="AL136" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM136" s="9">
+        <v>169</v>
+      </c>
+      <c r="AN136" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="137" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>407</v>
+      </c>
+      <c r="B137" t="s">
+        <v>408</v>
+      </c>
+      <c r="C137">
+        <v>24</v>
+      </c>
+      <c r="D137">
+        <v>3061</v>
+      </c>
+      <c r="E137" t="s">
+        <v>415</v>
+      </c>
+      <c r="F137">
+        <v>1</v>
+      </c>
+      <c r="G137" t="s">
+        <v>410</v>
+      </c>
+      <c r="H137" t="s">
+        <v>411</v>
+      </c>
+      <c r="K137">
+        <v>21</v>
+      </c>
+      <c r="O137" t="s">
+        <v>412</v>
+      </c>
+      <c r="P137">
+        <v>115</v>
+      </c>
+      <c r="Y137" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI137" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ137" s="9">
+        <v>21</v>
+      </c>
+      <c r="AK137" s="9">
+        <v>115</v>
+      </c>
+      <c r="AL137" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM137" s="9">
+        <v>136</v>
+      </c>
+      <c r="AN137" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="138" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>407</v>
+      </c>
+      <c r="B138" t="s">
+        <v>408</v>
+      </c>
+      <c r="C138">
+        <v>24</v>
+      </c>
+      <c r="D138">
+        <v>9082</v>
+      </c>
+      <c r="E138" t="s">
+        <v>415</v>
+      </c>
+      <c r="F138">
+        <v>2</v>
+      </c>
+      <c r="G138" t="s">
+        <v>410</v>
+      </c>
+      <c r="H138" t="s">
+        <v>411</v>
+      </c>
+      <c r="K138">
+        <v>3</v>
+      </c>
+      <c r="O138" t="s">
+        <v>412</v>
+      </c>
+      <c r="P138">
+        <v>18</v>
+      </c>
+      <c r="Y138" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI138" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ138" s="9">
+        <v>3</v>
+      </c>
+      <c r="AK138" s="9">
+        <v>18</v>
+      </c>
+      <c r="AL138" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM138" s="9">
+        <v>21</v>
+      </c>
+      <c r="AN138" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="139" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>407</v>
+      </c>
+      <c r="B139" t="s">
+        <v>408</v>
+      </c>
+      <c r="C139">
+        <v>24</v>
+      </c>
+      <c r="D139">
+        <v>112</v>
+      </c>
+      <c r="E139" t="s">
+        <v>415</v>
+      </c>
+      <c r="F139">
+        <v>3</v>
+      </c>
+      <c r="G139" t="s">
+        <v>410</v>
+      </c>
+      <c r="H139" t="s">
+        <v>411</v>
+      </c>
+      <c r="K139">
+        <v>28</v>
+      </c>
+      <c r="O139" t="s">
+        <v>412</v>
+      </c>
+      <c r="P139">
+        <v>93</v>
+      </c>
+      <c r="Y139" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI139" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ139" s="9">
+        <v>28</v>
+      </c>
+      <c r="AK139" s="9">
+        <v>93</v>
+      </c>
+      <c r="AL139" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM139" s="9">
+        <v>121</v>
+      </c>
+      <c r="AN139" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="140" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>407</v>
+      </c>
+      <c r="B140" t="s">
+        <v>408</v>
+      </c>
+      <c r="C140">
+        <v>25</v>
+      </c>
+      <c r="D140">
+        <v>2338</v>
+      </c>
+      <c r="E140" t="s">
+        <v>409</v>
+      </c>
+      <c r="F140">
+        <v>1</v>
+      </c>
+      <c r="G140" t="s">
+        <v>410</v>
+      </c>
+      <c r="H140" t="s">
+        <v>411</v>
+      </c>
+      <c r="K140">
+        <v>34</v>
+      </c>
+      <c r="O140" t="s">
+        <v>412</v>
+      </c>
+      <c r="P140">
+        <v>136</v>
+      </c>
+      <c r="Y140" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI140" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ140" s="9">
+        <v>34</v>
+      </c>
+      <c r="AK140" s="9">
+        <v>136</v>
+      </c>
+      <c r="AL140" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM140" s="9">
+        <v>170</v>
+      </c>
+      <c r="AN140" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="141" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>407</v>
+      </c>
+      <c r="B141" t="s">
+        <v>408</v>
+      </c>
+      <c r="C141">
+        <v>25</v>
+      </c>
+      <c r="D141">
+        <v>7457</v>
+      </c>
+      <c r="E141" t="s">
+        <v>409</v>
+      </c>
+      <c r="F141">
+        <v>2</v>
+      </c>
+      <c r="G141" t="s">
+        <v>410</v>
+      </c>
+      <c r="H141" t="s">
+        <v>411</v>
+      </c>
+      <c r="K141">
+        <v>39</v>
+      </c>
+      <c r="O141" t="s">
+        <v>412</v>
+      </c>
+      <c r="P141">
+        <v>192</v>
+      </c>
+      <c r="Y141" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI141" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ141" s="9">
+        <v>39</v>
+      </c>
+      <c r="AK141" s="9">
+        <v>192</v>
+      </c>
+      <c r="AL141" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM141" s="9">
+        <v>231</v>
+      </c>
+      <c r="AN141" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="142" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>407</v>
+      </c>
+      <c r="B142" t="s">
+        <v>408</v>
+      </c>
+      <c r="C142">
+        <v>25</v>
+      </c>
+      <c r="D142">
+        <v>1736</v>
+      </c>
+      <c r="E142" t="s">
+        <v>409</v>
+      </c>
+      <c r="F142">
+        <v>3</v>
+      </c>
+      <c r="G142" t="s">
+        <v>410</v>
+      </c>
+      <c r="H142" t="s">
+        <v>411</v>
+      </c>
+      <c r="K142">
+        <v>1</v>
+      </c>
+      <c r="O142" t="s">
+        <v>412</v>
+      </c>
+      <c r="P142">
+        <v>1</v>
+      </c>
+      <c r="Y142" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI142" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ142" s="9">
+        <v>1</v>
+      </c>
+      <c r="AK142" s="9">
+        <v>1</v>
+      </c>
+      <c r="AL142" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM142" s="9">
+        <v>2</v>
+      </c>
+      <c r="AN142" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="143" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>407</v>
+      </c>
+      <c r="B143" t="s">
+        <v>408</v>
+      </c>
+      <c r="C143">
+        <v>25</v>
+      </c>
+      <c r="D143">
+        <v>4256</v>
+      </c>
+      <c r="E143" t="s">
+        <v>415</v>
+      </c>
+      <c r="F143">
+        <v>1</v>
+      </c>
+      <c r="G143" t="s">
+        <v>410</v>
+      </c>
+      <c r="H143" t="s">
+        <v>411</v>
+      </c>
+      <c r="K143">
+        <v>2</v>
+      </c>
+      <c r="O143" t="s">
+        <v>412</v>
+      </c>
+      <c r="P143">
+        <v>73</v>
+      </c>
+      <c r="Y143" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI143" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ143" s="9">
+        <v>2</v>
+      </c>
+      <c r="AK143" s="9">
+        <v>73</v>
+      </c>
+      <c r="AL143" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM143" s="9">
+        <v>75</v>
+      </c>
+      <c r="AN143" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="144" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>407</v>
+      </c>
+      <c r="B144" t="s">
+        <v>408</v>
+      </c>
+      <c r="C144">
+        <v>25</v>
+      </c>
+      <c r="D144">
+        <v>1781</v>
+      </c>
+      <c r="E144" t="s">
+        <v>415</v>
+      </c>
+      <c r="F144">
+        <v>2</v>
+      </c>
+      <c r="G144" t="s">
+        <v>410</v>
+      </c>
+      <c r="H144" t="s">
+        <v>411</v>
+      </c>
+      <c r="K144">
+        <v>13</v>
+      </c>
+      <c r="O144" t="s">
+        <v>412</v>
+      </c>
+      <c r="P144">
+        <v>3</v>
+      </c>
+      <c r="Y144" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI144" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ144" s="9">
+        <v>13</v>
+      </c>
+      <c r="AK144" s="9">
+        <v>3</v>
+      </c>
+      <c r="AL144" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM144" s="9">
+        <v>16</v>
+      </c>
+      <c r="AN144" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="145" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>407</v>
+      </c>
+      <c r="B145" t="s">
+        <v>408</v>
+      </c>
+      <c r="C145">
+        <v>25</v>
+      </c>
+      <c r="D145">
+        <v>11173</v>
+      </c>
+      <c r="E145" t="s">
+        <v>415</v>
+      </c>
+      <c r="F145">
+        <v>3</v>
+      </c>
+      <c r="G145" t="s">
+        <v>410</v>
+      </c>
+      <c r="H145" t="s">
+        <v>411</v>
+      </c>
+      <c r="K145">
+        <v>42</v>
+      </c>
+      <c r="O145" t="s">
+        <v>412</v>
+      </c>
+      <c r="P145">
+        <v>42</v>
+      </c>
+      <c r="Y145" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI145" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ145" s="9">
+        <v>42</v>
+      </c>
+      <c r="AK145" s="9">
+        <v>42</v>
+      </c>
+      <c r="AL145" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM145" s="9">
+        <v>84</v>
+      </c>
+      <c r="AN145" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="146" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>407</v>
+      </c>
+      <c r="B146" t="s">
+        <v>408</v>
+      </c>
+      <c r="C146">
+        <v>26</v>
+      </c>
+      <c r="D146">
+        <v>1756</v>
+      </c>
+      <c r="E146" t="s">
+        <v>409</v>
+      </c>
+      <c r="F146">
+        <v>1</v>
+      </c>
+      <c r="G146" t="s">
+        <v>410</v>
+      </c>
+      <c r="H146" t="s">
+        <v>411</v>
+      </c>
+      <c r="K146">
+        <v>43</v>
+      </c>
+      <c r="O146" t="s">
+        <v>412</v>
+      </c>
+      <c r="P146">
+        <v>142</v>
+      </c>
+      <c r="Y146" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI146" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ146" s="9">
+        <v>43</v>
+      </c>
+      <c r="AK146" s="9">
+        <v>142</v>
+      </c>
+      <c r="AL146" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM146" s="9">
+        <v>185</v>
+      </c>
+      <c r="AN146" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="147" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>407</v>
+      </c>
+      <c r="B147" t="s">
+        <v>408</v>
+      </c>
+      <c r="C147">
+        <v>26</v>
+      </c>
+      <c r="D147">
+        <v>3397</v>
+      </c>
+      <c r="E147" t="s">
+        <v>409</v>
+      </c>
+      <c r="F147">
+        <v>2</v>
+      </c>
+      <c r="G147" t="s">
+        <v>410</v>
+      </c>
+      <c r="H147" t="s">
+        <v>411</v>
+      </c>
+      <c r="K147">
+        <v>1</v>
+      </c>
+      <c r="O147" t="s">
+        <v>412</v>
+      </c>
+      <c r="P147">
+        <v>20</v>
+      </c>
+      <c r="Y147" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI147" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ147" s="9">
+        <v>1</v>
+      </c>
+      <c r="AK147" s="9">
+        <v>20</v>
+      </c>
+      <c r="AL147" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM147" s="9">
+        <v>21</v>
+      </c>
+      <c r="AN147" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="148" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>407</v>
+      </c>
+      <c r="B148" t="s">
+        <v>408</v>
+      </c>
+      <c r="C148">
+        <v>26</v>
+      </c>
+      <c r="D148" t="s">
+        <v>420</v>
+      </c>
+      <c r="E148" t="s">
+        <v>409</v>
+      </c>
+      <c r="F148">
+        <v>3</v>
+      </c>
+      <c r="G148" t="s">
+        <v>410</v>
+      </c>
+      <c r="H148" t="s">
+        <v>411</v>
+      </c>
+      <c r="K148">
+        <v>2</v>
+      </c>
+      <c r="O148" t="s">
+        <v>412</v>
+      </c>
+      <c r="P148">
+        <v>65</v>
+      </c>
+      <c r="Y148" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI148" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ148" s="9">
+        <v>2</v>
+      </c>
+      <c r="AK148" s="9">
+        <v>65</v>
+      </c>
+      <c r="AL148" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM148" s="9">
+        <v>67</v>
+      </c>
+      <c r="AN148" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="149" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>407</v>
+      </c>
+      <c r="B149" t="s">
+        <v>408</v>
+      </c>
+      <c r="C149">
+        <v>26</v>
+      </c>
+      <c r="D149">
+        <v>2040</v>
+      </c>
+      <c r="E149" t="s">
+        <v>415</v>
+      </c>
+      <c r="F149">
+        <v>1</v>
+      </c>
+      <c r="G149" t="s">
+        <v>410</v>
+      </c>
+      <c r="H149" t="s">
+        <v>411</v>
+      </c>
+      <c r="K149">
+        <v>43</v>
+      </c>
+      <c r="O149" t="s">
+        <v>412</v>
+      </c>
+      <c r="P149">
+        <v>108</v>
+      </c>
+      <c r="Y149" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI149" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ149" s="9">
+        <v>43</v>
+      </c>
+      <c r="AK149" s="9">
+        <v>108</v>
+      </c>
+      <c r="AL149" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM149" s="9">
+        <v>151</v>
+      </c>
+      <c r="AN149" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="150" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>407</v>
+      </c>
+      <c r="B150" t="s">
+        <v>408</v>
+      </c>
+      <c r="C150">
+        <v>26</v>
+      </c>
+      <c r="D150">
+        <v>5125</v>
+      </c>
+      <c r="E150" t="s">
+        <v>415</v>
+      </c>
+      <c r="F150">
+        <v>2</v>
+      </c>
+      <c r="G150" t="s">
+        <v>410</v>
+      </c>
+      <c r="H150" t="s">
+        <v>411</v>
+      </c>
+      <c r="K150">
+        <v>1</v>
+      </c>
+      <c r="O150" t="s">
+        <v>412</v>
+      </c>
+      <c r="P150">
+        <v>42</v>
+      </c>
+      <c r="Y150" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI150" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ150" s="9">
+        <v>1</v>
+      </c>
+      <c r="AK150" s="9">
+        <v>42</v>
+      </c>
+      <c r="AL150" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM150" s="9">
+        <v>43</v>
+      </c>
+      <c r="AN150" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="151" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>407</v>
+      </c>
+      <c r="B151" t="s">
+        <v>408</v>
+      </c>
+      <c r="C151">
+        <v>26</v>
+      </c>
+      <c r="D151">
+        <v>1706</v>
+      </c>
+      <c r="E151" t="s">
+        <v>415</v>
+      </c>
+      <c r="F151">
+        <v>3</v>
+      </c>
+      <c r="G151" t="s">
+        <v>410</v>
+      </c>
+      <c r="H151" t="s">
+        <v>411</v>
+      </c>
+      <c r="K151">
+        <v>61</v>
+      </c>
+      <c r="O151" t="s">
+        <v>412</v>
+      </c>
+      <c r="P151">
+        <v>259</v>
+      </c>
+      <c r="Y151" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI151" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ151" s="9">
+        <v>61</v>
+      </c>
+      <c r="AK151" s="9">
+        <v>259</v>
+      </c>
+      <c r="AL151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM151" s="9">
+        <v>320</v>
+      </c>
+      <c r="AN151" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="152" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>407</v>
+      </c>
+      <c r="B152" t="s">
+        <v>408</v>
+      </c>
+      <c r="C152">
+        <v>27</v>
+      </c>
+      <c r="D152">
+        <v>9401</v>
+      </c>
+      <c r="E152" t="s">
+        <v>409</v>
+      </c>
+      <c r="F152">
+        <v>1</v>
+      </c>
+      <c r="G152" t="s">
+        <v>410</v>
+      </c>
+      <c r="H152" t="s">
+        <v>411</v>
+      </c>
+      <c r="K152">
+        <v>51</v>
+      </c>
+      <c r="O152" t="s">
+        <v>412</v>
+      </c>
+      <c r="P152">
+        <v>172</v>
+      </c>
+      <c r="Y152" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI152" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ152" s="9">
+        <v>51</v>
+      </c>
+      <c r="AK152" s="9">
+        <v>172</v>
+      </c>
+      <c r="AL152" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM152" s="9">
+        <v>223</v>
+      </c>
+      <c r="AN152" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="153" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>407</v>
+      </c>
+      <c r="B153" t="s">
+        <v>408</v>
+      </c>
+      <c r="C153">
+        <v>27</v>
+      </c>
+      <c r="D153">
+        <v>648</v>
+      </c>
+      <c r="E153" t="s">
+        <v>409</v>
+      </c>
+      <c r="F153">
+        <v>2</v>
+      </c>
+      <c r="G153" t="s">
+        <v>410</v>
+      </c>
+      <c r="H153" t="s">
+        <v>411</v>
+      </c>
+      <c r="K153">
+        <v>22</v>
+      </c>
+      <c r="O153" t="s">
+        <v>412</v>
+      </c>
+      <c r="P153">
+        <v>124</v>
+      </c>
+      <c r="Y153" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI153" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ153" s="9">
+        <v>22</v>
+      </c>
+      <c r="AK153" s="9">
+        <v>124</v>
+      </c>
+      <c r="AL153" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM153" s="9">
+        <v>146</v>
+      </c>
+      <c r="AN153" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="154" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>407</v>
+      </c>
+      <c r="B154" t="s">
+        <v>408</v>
+      </c>
+      <c r="C154">
+        <v>27</v>
+      </c>
+      <c r="D154">
+        <v>1306</v>
+      </c>
+      <c r="E154" t="s">
+        <v>409</v>
+      </c>
+      <c r="F154">
+        <v>3</v>
+      </c>
+      <c r="G154" t="s">
+        <v>410</v>
+      </c>
+      <c r="H154" t="s">
+        <v>411</v>
+      </c>
+      <c r="K154">
+        <v>32</v>
+      </c>
+      <c r="O154" t="s">
+        <v>412</v>
+      </c>
+      <c r="P154">
+        <v>201</v>
+      </c>
+      <c r="Y154" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI154" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ154" s="9">
+        <v>32</v>
+      </c>
+      <c r="AK154" s="9">
+        <v>201</v>
+      </c>
+      <c r="AL154" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM154" s="9">
+        <v>233</v>
+      </c>
+      <c r="AN154" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="155" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>407</v>
+      </c>
+      <c r="B155" t="s">
+        <v>408</v>
+      </c>
+      <c r="C155">
+        <v>27</v>
+      </c>
+      <c r="D155">
+        <v>3061</v>
+      </c>
+      <c r="E155" t="s">
+        <v>415</v>
+      </c>
+      <c r="F155">
+        <v>1</v>
+      </c>
+      <c r="G155" t="s">
+        <v>410</v>
+      </c>
+      <c r="H155" t="s">
+        <v>411</v>
+      </c>
+      <c r="K155">
+        <v>29</v>
+      </c>
+      <c r="O155" t="s">
+        <v>412</v>
+      </c>
+      <c r="P155">
+        <v>123</v>
+      </c>
+      <c r="Y155" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI155" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ155" s="9">
+        <v>29</v>
+      </c>
+      <c r="AK155" s="9">
+        <v>123</v>
+      </c>
+      <c r="AL155" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM155" s="9">
+        <v>152</v>
+      </c>
+      <c r="AN155" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="156" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>407</v>
+      </c>
+      <c r="B156" t="s">
+        <v>408</v>
+      </c>
+      <c r="C156">
+        <v>27</v>
+      </c>
+      <c r="D156">
+        <v>4655</v>
+      </c>
+      <c r="E156" t="s">
+        <v>415</v>
+      </c>
+      <c r="F156">
+        <v>2</v>
+      </c>
+      <c r="G156" t="s">
+        <v>410</v>
+      </c>
+      <c r="H156" t="s">
+        <v>411</v>
+      </c>
+      <c r="K156">
+        <v>28</v>
+      </c>
+      <c r="O156" t="s">
+        <v>412</v>
+      </c>
+      <c r="P156">
+        <v>96</v>
+      </c>
+      <c r="Y156" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI156" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ156" s="9">
+        <v>28</v>
+      </c>
+      <c r="AK156" s="9">
+        <v>96</v>
+      </c>
+      <c r="AL156" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM156" s="9">
+        <v>124</v>
+      </c>
+      <c r="AN156" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="157" spans="1:40" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>407</v>
+      </c>
+      <c r="B157" t="s">
+        <v>408</v>
+      </c>
+      <c r="C157">
+        <v>27</v>
+      </c>
+      <c r="D157">
+        <v>5934</v>
+      </c>
+      <c r="E157" t="s">
+        <v>415</v>
+      </c>
+      <c r="F157">
+        <v>3</v>
+      </c>
+      <c r="G157" t="s">
+        <v>410</v>
+      </c>
+      <c r="H157" t="s">
+        <v>411</v>
+      </c>
+      <c r="K157">
+        <v>31</v>
+      </c>
+      <c r="O157" t="s">
+        <v>412</v>
+      </c>
+      <c r="P157">
+        <v>49</v>
+      </c>
+      <c r="Y157" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI157" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ157" s="9">
+        <v>31</v>
+      </c>
+      <c r="AK157" s="9">
+        <v>49</v>
+      </c>
+      <c r="AL157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AM157" s="9">
+        <v>80</v>
+      </c>
+      <c r="AN157" t="s">
+        <v>443</v>
       </c>
     </row>
   </sheetData>
@@ -8058,7 +11448,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23E27264-59F9-4DC3-8DE6-549047E78D3C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A94E1CC3-AE48-4216-821C-34B059A52177}">
   <dimension ref="A1:AC304"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -8209,15 +11599,15 @@
       </c>
       <c r="B5" s="12" cm="1">
         <f t="array" ref="B5:B39">IF(_xlfn.ANCHORARRAY(A5)="","",COUNTIFS(Scans[Team '#],_xlfn.ANCHORARRAY(A5)))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" s="13" cm="1">
         <f t="array" ref="C5:C39">IF(_xlfn.ANCHORARRAY(A5)="","",AVERAGEIFS(Scans[Auto pts],Scans[Team '#],_xlfn.ANCHORARRAY(A5)))</f>
-        <v>40.666666666666664</v>
+        <v>26.75</v>
       </c>
       <c r="D5" s="13" cm="1">
         <f t="array" ref="D5:D39">IF(_xlfn.ANCHORARRAY(A5)="","",AVERAGEIFS(Scans[Teleop fuel pts],Scans[Team '#],_xlfn.ANCHORARRAY(A5)))</f>
-        <v>77.333333333333329</v>
+        <v>41</v>
       </c>
       <c r="E5" s="13" cm="1">
         <f t="array" ref="E5:E39">IF(_xlfn.ANCHORARRAY(A5)="","",AVERAGEIFS(Scans[Climb pts],Scans[Team '#],_xlfn.ANCHORARRAY(A5)))</f>
@@ -8225,11 +11615,11 @@
       </c>
       <c r="F5" s="13" cm="1">
         <f t="array" ref="F5:F39">IF(_xlfn.ANCHORARRAY(A5)="","",AVERAGEIFS(Scans[Total pts],Scans[Team '#],_xlfn.ANCHORARRAY(A5)))</f>
-        <v>118</v>
+        <v>67.75</v>
       </c>
       <c r="G5" s="12" cm="1">
         <f t="array" ref="G5:G39">IF(_xlfn.ANCHORARRAY(A5)="","",_xlfn.MAXIFS(Scans[Total pts],Scans[Team '#],_xlfn.ANCHORARRAY(A5)))</f>
-        <v>134</v>
+        <v>76</v>
       </c>
       <c r="H5" s="14" cm="1">
         <f t="array" ref="H5:H39">IF(_xlfn.ANCHORARRAY(A5)="","",IFERROR((SUMIFS(Scans[Auto fuel scored],Scans[Team '#],_xlfn.ANCHORARRAY(A5))+SUMIFS(Scans[Teleop fuel scored],Scans[Team '#],_xlfn.ANCHORARRAY(A5)))/(SUMIFS(Scans[Auto fuel scored],Scans[Team '#],_xlfn.ANCHORARRAY(A5))+SUMIFS(Scans[Teleop fuel scored],Scans[Team '#],_xlfn.ANCHORARRAY(A5))+SUMIFS(Scans[Auto fuel missed],Scans[Team '#],_xlfn.ANCHORARRAY(A5))+SUMIFS(Scans[Teleop fuel missed],Scans[Team '#],_xlfn.ANCHORARRAY(A5))),""))</f>
@@ -8273,7 +11663,7 @@
       </c>
       <c r="R5" s="12" cm="1">
         <f t="array" ref="R5:R39">IF(_xlfn.ANCHORARRAY(A5)="","",_xlfn.RANK.EQ(_xlfn.ANCHORARRAY(F5),_xlfn.ANCHORARRAY(F5)))</f>
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="T5" s="15" cm="1">
         <f t="array" ref="T5:T39">IF(A5="","",_xlfn.SEQUENCE(ROWS(_xlfn.ANCHORARRAY(A5))))</f>
@@ -8284,13 +11674,13 @@
         <v>1706</v>
       </c>
       <c r="V5" s="13">
-        <v>268.5</v>
+        <v>314.25</v>
       </c>
       <c r="W5" s="13">
-        <v>66.5</v>
+        <v>62</v>
       </c>
       <c r="X5" s="13">
-        <v>202</v>
+        <v>252.25</v>
       </c>
       <c r="Y5" s="13">
         <v>0</v>
@@ -8313,22 +11703,22 @@
         <v>112</v>
       </c>
       <c r="B6" s="12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C6" s="13">
-        <v>19.333333333333332</v>
+        <v>33.200000000000003</v>
       </c>
       <c r="D6" s="13">
-        <v>57.666666666666664</v>
+        <v>103.2</v>
       </c>
       <c r="E6" s="13">
         <v>0</v>
       </c>
       <c r="F6" s="13">
-        <v>77</v>
+        <v>136.4</v>
       </c>
       <c r="G6" s="12">
-        <v>92</v>
+        <v>168</v>
       </c>
       <c r="H6" s="14">
         <v>1</v>
@@ -8361,7 +11751,7 @@
         <v>0</v>
       </c>
       <c r="R6" s="12">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="T6" s="15">
         <v>2</v>
@@ -8370,13 +11760,13 @@
         <v>2481</v>
       </c>
       <c r="V6" s="13">
-        <v>261.66666666666669</v>
+        <v>296.75</v>
       </c>
       <c r="W6" s="13">
-        <v>46.333333333333336</v>
+        <v>49.5</v>
       </c>
       <c r="X6" s="13">
-        <v>215.33333333333334</v>
+        <v>247.25</v>
       </c>
       <c r="Y6" s="13">
         <v>0</v>
@@ -8399,22 +11789,22 @@
         <v>648</v>
       </c>
       <c r="B7" s="12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C7" s="13">
-        <v>13</v>
+        <v>16.2</v>
       </c>
       <c r="D7" s="13">
-        <v>46</v>
+        <v>102</v>
       </c>
       <c r="E7" s="13">
         <v>0</v>
       </c>
       <c r="F7" s="13">
-        <v>59</v>
+        <v>118.2</v>
       </c>
       <c r="G7" s="12">
-        <v>71</v>
+        <v>146</v>
       </c>
       <c r="H7" s="14">
         <v>1</v>
@@ -8447,22 +11837,22 @@
         <v>0</v>
       </c>
       <c r="R7" s="12">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="T7" s="15">
         <v>3</v>
       </c>
       <c r="U7" s="16">
-        <v>930</v>
+        <v>7457</v>
       </c>
       <c r="V7" s="13">
-        <v>205.33333333333334</v>
+        <v>239</v>
       </c>
       <c r="W7" s="13">
-        <v>42.666666666666664</v>
+        <v>43.2</v>
       </c>
       <c r="X7" s="13">
-        <v>162.66666666666666</v>
+        <v>195.8</v>
       </c>
       <c r="Y7" s="13">
         <v>0</v>
@@ -8485,22 +11875,22 @@
         <v>930</v>
       </c>
       <c r="B8" s="12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C8" s="13">
-        <v>42.666666666666664</v>
+        <v>45</v>
       </c>
       <c r="D8" s="13">
-        <v>162.66666666666666</v>
+        <v>132.4</v>
       </c>
       <c r="E8" s="13">
         <v>0</v>
       </c>
       <c r="F8" s="13">
-        <v>205.33333333333334</v>
+        <v>177.4</v>
       </c>
       <c r="G8" s="12">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="H8" s="14">
         <v>1</v>
@@ -8533,7 +11923,7 @@
         <v>0</v>
       </c>
       <c r="R8" s="12">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T8" s="15">
         <v>4</v>
@@ -8542,13 +11932,13 @@
         <v>1306</v>
       </c>
       <c r="V8" s="13">
-        <v>192</v>
+        <v>207.25</v>
       </c>
       <c r="W8" s="13">
-        <v>15.666666666666666</v>
+        <v>25.75</v>
       </c>
       <c r="X8" s="13">
-        <v>176.33333333333334</v>
+        <v>181.5</v>
       </c>
       <c r="Y8" s="13">
         <v>0</v>
@@ -8571,22 +11961,22 @@
         <v>1306</v>
       </c>
       <c r="B9" s="12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" s="13">
-        <v>15.666666666666666</v>
+        <v>25.75</v>
       </c>
       <c r="D9" s="13">
-        <v>176.33333333333334</v>
+        <v>181.5</v>
       </c>
       <c r="E9" s="13">
         <v>0</v>
       </c>
       <c r="F9" s="13">
-        <v>192</v>
+        <v>207.25</v>
       </c>
       <c r="G9" s="12">
-        <v>203</v>
+        <v>233</v>
       </c>
       <c r="H9" s="14">
         <v>1</v>
@@ -8625,16 +12015,16 @@
         <v>5</v>
       </c>
       <c r="U9" s="16">
-        <v>4096</v>
+        <v>9401</v>
       </c>
       <c r="V9" s="13">
-        <v>191.33333333333334</v>
+        <v>194.2</v>
       </c>
       <c r="W9" s="13">
-        <v>19.666666666666668</v>
+        <v>41.4</v>
       </c>
       <c r="X9" s="13">
-        <v>171.66666666666666</v>
+        <v>152.80000000000001</v>
       </c>
       <c r="Y9" s="13">
         <v>0</v>
@@ -8657,22 +12047,22 @@
         <v>1625</v>
       </c>
       <c r="B10" s="12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" s="13">
-        <v>8.3333333333333339</v>
+        <v>3.5</v>
       </c>
       <c r="D10" s="13">
-        <v>65</v>
+        <v>75.75</v>
       </c>
       <c r="E10" s="13">
         <v>0</v>
       </c>
       <c r="F10" s="13">
-        <v>73.333333333333329</v>
+        <v>79.25</v>
       </c>
       <c r="G10" s="12">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="H10" s="14">
         <v>1</v>
@@ -8705,22 +12095,22 @@
         <v>0</v>
       </c>
       <c r="R10" s="12">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="T10" s="15">
         <v>6</v>
       </c>
       <c r="U10" s="16">
-        <v>7457</v>
+        <v>1756</v>
       </c>
       <c r="V10" s="13">
-        <v>188.66666666666666</v>
+        <v>189.2</v>
       </c>
       <c r="W10" s="13">
-        <v>50.666666666666664</v>
+        <v>40.4</v>
       </c>
       <c r="X10" s="13">
-        <v>138</v>
+        <v>148.80000000000001</v>
       </c>
       <c r="Y10" s="13">
         <v>0</v>
@@ -8743,22 +12133,22 @@
         <v>1706</v>
       </c>
       <c r="B11" s="12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C11" s="13">
-        <v>66.5</v>
+        <v>62</v>
       </c>
       <c r="D11" s="13">
-        <v>202</v>
+        <v>252.25</v>
       </c>
       <c r="E11" s="13">
         <v>0</v>
       </c>
       <c r="F11" s="13">
-        <v>268.5</v>
+        <v>314.25</v>
       </c>
       <c r="G11" s="12">
-        <v>272</v>
+        <v>320</v>
       </c>
       <c r="H11" s="14">
         <v>1</v>
@@ -8797,16 +12187,16 @@
         <v>7</v>
       </c>
       <c r="U11" s="16">
-        <v>7117</v>
+        <v>930</v>
       </c>
       <c r="V11" s="13">
-        <v>182</v>
+        <v>177.4</v>
       </c>
       <c r="W11" s="13">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="X11" s="13">
-        <v>123</v>
+        <v>132.4</v>
       </c>
       <c r="Y11" s="13">
         <v>0</v>
@@ -8829,22 +12219,22 @@
         <v>1736</v>
       </c>
       <c r="B12" s="12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C12" s="13">
-        <v>5.333333333333333</v>
+        <v>0.6</v>
       </c>
       <c r="D12" s="13">
-        <v>33</v>
+        <v>0.8</v>
       </c>
       <c r="E12" s="13">
         <v>0</v>
       </c>
       <c r="F12" s="13">
-        <v>38.333333333333336</v>
+        <v>1.4</v>
       </c>
       <c r="G12" s="12">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="H12" s="14">
         <v>1</v>
@@ -8877,22 +12267,22 @@
         <v>0</v>
       </c>
       <c r="R12" s="12">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="T12" s="15">
         <v>8</v>
       </c>
       <c r="U12" s="16">
-        <v>3061</v>
+        <v>2338</v>
       </c>
       <c r="V12" s="13">
-        <v>176.33333333333334</v>
+        <v>174.4</v>
       </c>
       <c r="W12" s="13">
-        <v>27</v>
+        <v>36.6</v>
       </c>
       <c r="X12" s="13">
-        <v>149.33333333333334</v>
+        <v>137.80000000000001</v>
       </c>
       <c r="Y12" s="13">
         <v>0</v>
@@ -8915,22 +12305,22 @@
         <v>1756</v>
       </c>
       <c r="B13" s="12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C13" s="13">
-        <v>34.333333333333336</v>
+        <v>40.4</v>
       </c>
       <c r="D13" s="13">
-        <v>120.33333333333333</v>
+        <v>148.80000000000001</v>
       </c>
       <c r="E13" s="13">
         <v>0</v>
       </c>
       <c r="F13" s="13">
-        <v>154.66666666666666</v>
+        <v>189.2</v>
       </c>
       <c r="G13" s="12">
-        <v>162</v>
+        <v>213</v>
       </c>
       <c r="H13" s="14">
         <v>1</v>
@@ -8963,22 +12353,22 @@
         <v>0</v>
       </c>
       <c r="R13" s="12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T13" s="15">
         <v>9</v>
       </c>
-      <c r="U13" s="16">
-        <v>2338</v>
+      <c r="U13" s="16" t="str">
+        <v>1706B</v>
       </c>
       <c r="V13" s="13">
-        <v>158.5</v>
+        <v>159.4</v>
       </c>
       <c r="W13" s="13">
-        <v>24.5</v>
+        <v>35.4</v>
       </c>
       <c r="X13" s="13">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="Y13" s="13">
         <v>0</v>
@@ -9001,22 +12391,22 @@
         <v>1781</v>
       </c>
       <c r="B14" s="12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C14" s="13">
-        <v>3.3333333333333335</v>
+        <v>7.4</v>
       </c>
       <c r="D14" s="13">
-        <v>44.666666666666664</v>
+        <v>3.4</v>
       </c>
       <c r="E14" s="13">
         <v>0</v>
       </c>
       <c r="F14" s="13">
-        <v>48</v>
+        <v>10.8</v>
       </c>
       <c r="G14" s="12">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="H14" s="14">
         <v>1</v>
@@ -9049,22 +12439,22 @@
         <v>0</v>
       </c>
       <c r="R14" s="12">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="T14" s="15">
         <v>10</v>
       </c>
       <c r="U14" s="16">
-        <v>1756</v>
+        <v>4096</v>
       </c>
       <c r="V14" s="13">
-        <v>154.66666666666666</v>
+        <v>156.5</v>
       </c>
       <c r="W14" s="13">
-        <v>34.333333333333336</v>
+        <v>10.25</v>
       </c>
       <c r="X14" s="13">
-        <v>120.33333333333333</v>
+        <v>146.25</v>
       </c>
       <c r="Y14" s="13">
         <v>0</v>
@@ -9087,22 +12477,22 @@
         <v>1792</v>
       </c>
       <c r="B15" s="12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C15" s="13">
-        <v>36.5</v>
+        <v>34.75</v>
       </c>
       <c r="D15" s="13">
-        <v>67</v>
+        <v>54.5</v>
       </c>
       <c r="E15" s="13">
         <v>0</v>
       </c>
       <c r="F15" s="13">
-        <v>103.5</v>
+        <v>89.25</v>
       </c>
       <c r="G15" s="12">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="H15" s="14">
         <v>1</v>
@@ -9135,22 +12525,22 @@
         <v>0</v>
       </c>
       <c r="R15" s="12">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="T15" s="15">
         <v>11</v>
       </c>
       <c r="U15" s="16">
-        <v>5847</v>
+        <v>3061</v>
       </c>
       <c r="V15" s="13">
-        <v>128</v>
+        <v>154.6</v>
       </c>
       <c r="W15" s="13">
-        <v>25.666666666666668</v>
+        <v>25.4</v>
       </c>
       <c r="X15" s="13">
-        <v>102.33333333333333</v>
+        <v>129.19999999999999</v>
       </c>
       <c r="Y15" s="13">
         <v>0</v>
@@ -9173,22 +12563,22 @@
         <v>2040</v>
       </c>
       <c r="B16" s="12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" s="13">
-        <v>30.333333333333332</v>
+        <v>40.6</v>
       </c>
       <c r="D16" s="13">
-        <v>87.333333333333329</v>
+        <v>97.8</v>
       </c>
       <c r="E16" s="13">
         <v>0</v>
       </c>
       <c r="F16" s="13">
-        <v>117.66666666666667</v>
+        <v>138.4</v>
       </c>
       <c r="G16" s="12">
-        <v>134</v>
+        <v>167</v>
       </c>
       <c r="H16" s="14">
         <v>1</v>
@@ -9221,22 +12611,22 @@
         <v>0</v>
       </c>
       <c r="R16" s="12">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="T16" s="15">
         <v>12</v>
       </c>
       <c r="U16" s="16">
-        <v>5934</v>
+        <v>2040</v>
       </c>
       <c r="V16" s="13">
-        <v>118.5</v>
+        <v>138.4</v>
       </c>
       <c r="W16" s="13">
-        <v>14.5</v>
+        <v>40.6</v>
       </c>
       <c r="X16" s="13">
-        <v>104</v>
+        <v>97.8</v>
       </c>
       <c r="Y16" s="13">
         <v>0</v>
@@ -9259,22 +12649,22 @@
         <v>2290</v>
       </c>
       <c r="B17" s="12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C17" s="13">
-        <v>23.666666666666668</v>
+        <v>10.25</v>
       </c>
       <c r="D17" s="13">
-        <v>78.666666666666671</v>
+        <v>11.25</v>
       </c>
       <c r="E17" s="13">
         <v>0</v>
       </c>
       <c r="F17" s="13">
-        <v>102.33333333333333</v>
+        <v>21.5</v>
       </c>
       <c r="G17" s="12">
-        <v>110</v>
+        <v>27</v>
       </c>
       <c r="H17" s="14">
         <v>1</v>
@@ -9307,22 +12697,22 @@
         <v>0</v>
       </c>
       <c r="R17" s="12">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="T17" s="15">
         <v>13</v>
       </c>
       <c r="U17" s="16">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="V17" s="13">
-        <v>118</v>
+        <v>136.4</v>
       </c>
       <c r="W17" s="13">
-        <v>40.666666666666664</v>
+        <v>33.200000000000003</v>
       </c>
       <c r="X17" s="13">
-        <v>77.333333333333329</v>
+        <v>103.2</v>
       </c>
       <c r="Y17" s="13">
         <v>0</v>
@@ -9345,22 +12735,22 @@
         <v>2338</v>
       </c>
       <c r="B18" s="12">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C18" s="13">
-        <v>24.5</v>
+        <v>36.6</v>
       </c>
       <c r="D18" s="13">
-        <v>134</v>
+        <v>137.80000000000001</v>
       </c>
       <c r="E18" s="13">
         <v>0</v>
       </c>
       <c r="F18" s="13">
-        <v>158.5</v>
+        <v>174.4</v>
       </c>
       <c r="G18" s="12">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="H18" s="14">
         <v>1</v>
@@ -9393,22 +12783,22 @@
         <v>0</v>
       </c>
       <c r="R18" s="12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T18" s="15">
         <v>14</v>
       </c>
       <c r="U18" s="16">
-        <v>2040</v>
+        <v>4655</v>
       </c>
       <c r="V18" s="13">
-        <v>117.66666666666667</v>
+        <v>124</v>
       </c>
       <c r="W18" s="13">
-        <v>30.333333333333332</v>
+        <v>24.6</v>
       </c>
       <c r="X18" s="13">
-        <v>87.333333333333329</v>
+        <v>99.4</v>
       </c>
       <c r="Y18" s="13">
         <v>0</v>
@@ -9431,22 +12821,22 @@
         <v>2481</v>
       </c>
       <c r="B19" s="12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C19" s="13">
-        <v>46.333333333333336</v>
+        <v>49.5</v>
       </c>
       <c r="D19" s="13">
-        <v>215.33333333333334</v>
+        <v>247.25</v>
       </c>
       <c r="E19" s="13">
         <v>0</v>
       </c>
       <c r="F19" s="13">
-        <v>261.66666666666669</v>
+        <v>296.75</v>
       </c>
       <c r="G19" s="12">
-        <v>269</v>
+        <v>307</v>
       </c>
       <c r="H19" s="14">
         <v>1</v>
@@ -9485,16 +12875,16 @@
         <v>15</v>
       </c>
       <c r="U19" s="16">
-        <v>4256</v>
+        <v>648</v>
       </c>
       <c r="V19" s="13">
-        <v>112.66666666666667</v>
+        <v>118.2</v>
       </c>
       <c r="W19" s="13">
-        <v>1</v>
+        <v>16.2</v>
       </c>
       <c r="X19" s="13">
-        <v>111.66666666666667</v>
+        <v>102</v>
       </c>
       <c r="Y19" s="13">
         <v>0</v>
@@ -9517,22 +12907,22 @@
         <v>3061</v>
       </c>
       <c r="B20" s="12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C20" s="13">
-        <v>27</v>
+        <v>25.4</v>
       </c>
       <c r="D20" s="13">
-        <v>149.33333333333334</v>
+        <v>129.19999999999999</v>
       </c>
       <c r="E20" s="13">
         <v>0</v>
       </c>
       <c r="F20" s="13">
-        <v>176.33333333333334</v>
+        <v>154.6</v>
       </c>
       <c r="G20" s="12">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="H20" s="14">
         <v>1</v>
@@ -9565,22 +12955,22 @@
         <v>0</v>
       </c>
       <c r="R20" s="12">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T20" s="15">
         <v>16</v>
       </c>
-      <c r="U20" s="16" t="str">
-        <v>1706B</v>
+      <c r="U20" s="16">
+        <v>7117</v>
       </c>
       <c r="V20" s="13">
         <v>105.5</v>
       </c>
       <c r="W20" s="13">
-        <v>11.5</v>
+        <v>35.75</v>
       </c>
       <c r="X20" s="13">
-        <v>94</v>
+        <v>69.75</v>
       </c>
       <c r="Y20" s="13">
         <v>0</v>
@@ -9603,22 +12993,22 @@
         <v>3197</v>
       </c>
       <c r="B21" s="12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C21" s="13">
-        <v>8</v>
+        <v>9.25</v>
       </c>
       <c r="D21" s="13">
-        <v>75</v>
+        <v>57.75</v>
       </c>
       <c r="E21" s="13">
         <v>0</v>
       </c>
       <c r="F21" s="13">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="G21" s="12">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H21" s="14">
         <v>1</v>
@@ -9651,22 +13041,22 @@
         <v>0</v>
       </c>
       <c r="R21" s="12">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="T21" s="15">
         <v>17</v>
       </c>
       <c r="U21" s="16">
-        <v>1792</v>
+        <v>5847</v>
       </c>
       <c r="V21" s="13">
-        <v>103.5</v>
+        <v>98.666666666666671</v>
       </c>
       <c r="W21" s="13">
-        <v>36.5</v>
+        <v>14.333333333333334</v>
       </c>
       <c r="X21" s="13">
-        <v>67</v>
+        <v>84.333333333333329</v>
       </c>
       <c r="Y21" s="13">
         <v>0</v>
@@ -9689,22 +13079,22 @@
         <v>3397</v>
       </c>
       <c r="B22" s="12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C22" s="13">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="D22" s="13">
-        <v>5.666666666666667</v>
+        <v>18.8</v>
       </c>
       <c r="E22" s="13">
         <v>0</v>
       </c>
       <c r="F22" s="13">
-        <v>6.666666666666667</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="G22" s="12">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="H22" s="14">
         <v>1</v>
@@ -9737,22 +13127,22 @@
         <v>0</v>
       </c>
       <c r="R22" s="12">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="T22" s="15">
         <v>18</v>
       </c>
       <c r="U22" s="16">
-        <v>2290</v>
+        <v>4256</v>
       </c>
       <c r="V22" s="13">
-        <v>102.33333333333333</v>
+        <v>94</v>
       </c>
       <c r="W22" s="13">
-        <v>23.666666666666668</v>
+        <v>1.25</v>
       </c>
       <c r="X22" s="13">
-        <v>78.666666666666671</v>
+        <v>92.75</v>
       </c>
       <c r="Y22" s="13">
         <v>0</v>
@@ -9775,22 +13165,22 @@
         <v>4096</v>
       </c>
       <c r="B23" s="12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C23" s="13">
-        <v>19.666666666666668</v>
+        <v>10.25</v>
       </c>
       <c r="D23" s="13">
-        <v>171.66666666666666</v>
+        <v>146.25</v>
       </c>
       <c r="E23" s="13">
         <v>0</v>
       </c>
       <c r="F23" s="13">
-        <v>191.33333333333334</v>
+        <v>156.5</v>
       </c>
       <c r="G23" s="12">
-        <v>196</v>
+        <v>159</v>
       </c>
       <c r="H23" s="14">
         <v>1</v>
@@ -9823,22 +13213,22 @@
         <v>0</v>
       </c>
       <c r="R23" s="12">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" s="15">
         <v>19</v>
       </c>
       <c r="U23" s="16">
-        <v>9401</v>
+        <v>1792</v>
       </c>
       <c r="V23" s="13">
-        <v>95</v>
+        <v>89.25</v>
       </c>
       <c r="W23" s="13">
-        <v>11.5</v>
+        <v>34.75</v>
       </c>
       <c r="X23" s="13">
-        <v>83.5</v>
+        <v>54.5</v>
       </c>
       <c r="Y23" s="13">
         <v>0</v>
@@ -9861,22 +13251,22 @@
         <v>4143</v>
       </c>
       <c r="B24" s="12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C24" s="13">
-        <v>9.5</v>
+        <v>3</v>
       </c>
       <c r="D24" s="13">
-        <v>51</v>
+        <v>48.5</v>
       </c>
       <c r="E24" s="13">
         <v>0</v>
       </c>
       <c r="F24" s="13">
-        <v>60.5</v>
+        <v>51.5</v>
       </c>
       <c r="G24" s="12">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="H24" s="14">
         <v>1</v>
@@ -9915,16 +13305,16 @@
         <v>20</v>
       </c>
       <c r="U24" s="16">
-        <v>4655</v>
+        <v>1625</v>
       </c>
       <c r="V24" s="13">
-        <v>88</v>
+        <v>79.25</v>
       </c>
       <c r="W24" s="13">
-        <v>7.333333333333333</v>
+        <v>3.5</v>
       </c>
       <c r="X24" s="13">
-        <v>80.666666666666671</v>
+        <v>75.75</v>
       </c>
       <c r="Y24" s="13">
         <v>0</v>
@@ -9947,22 +13337,22 @@
         <v>4256</v>
       </c>
       <c r="B25" s="12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C25" s="13">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="D25" s="13">
-        <v>111.66666666666667</v>
+        <v>92.75</v>
       </c>
       <c r="E25" s="13">
         <v>0</v>
       </c>
       <c r="F25" s="13">
-        <v>112.66666666666667</v>
+        <v>94</v>
       </c>
       <c r="G25" s="12">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="H25" s="14">
         <v>1</v>
@@ -9995,22 +13385,22 @@
         <v>0</v>
       </c>
       <c r="R25" s="12">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="T25" s="15">
         <v>21</v>
       </c>
       <c r="U25" s="16">
-        <v>3197</v>
+        <v>11173</v>
       </c>
       <c r="V25" s="13">
-        <v>83</v>
+        <v>77.8</v>
       </c>
       <c r="W25" s="13">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="X25" s="13">
-        <v>75</v>
+        <v>51.8</v>
       </c>
       <c r="Y25" s="13">
         <v>0</v>
@@ -10033,19 +13423,19 @@
         <v>4423</v>
       </c>
       <c r="B26" s="12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C26" s="13">
-        <v>5.5</v>
+        <v>2.75</v>
       </c>
       <c r="D26" s="13">
-        <v>18.5</v>
+        <v>22.5</v>
       </c>
       <c r="E26" s="13">
         <v>0</v>
       </c>
       <c r="F26" s="13">
-        <v>24</v>
+        <v>25.25</v>
       </c>
       <c r="G26" s="12">
         <v>28</v>
@@ -10081,22 +13471,22 @@
         <v>0</v>
       </c>
       <c r="R26" s="12">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="T26" s="15">
         <v>22</v>
       </c>
       <c r="U26" s="16">
-        <v>11173</v>
+        <v>5934</v>
       </c>
       <c r="V26" s="13">
-        <v>78</v>
+        <v>75.8</v>
       </c>
       <c r="W26" s="13">
-        <v>10.333333333333334</v>
+        <v>25.2</v>
       </c>
       <c r="X26" s="13">
-        <v>67.666666666666671</v>
+        <v>50.6</v>
       </c>
       <c r="Y26" s="13">
         <v>0</v>
@@ -10119,22 +13509,22 @@
         <v>4655</v>
       </c>
       <c r="B27" s="12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C27" s="13">
-        <v>7.333333333333333</v>
+        <v>24.6</v>
       </c>
       <c r="D27" s="13">
-        <v>80.666666666666671</v>
+        <v>99.4</v>
       </c>
       <c r="E27" s="13">
         <v>0</v>
       </c>
       <c r="F27" s="13">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="G27" s="12">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="H27" s="14">
         <v>1</v>
@@ -10167,22 +13557,22 @@
         <v>0</v>
       </c>
       <c r="R27" s="12">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="T27" s="15">
         <v>23</v>
       </c>
-      <c r="U27" s="16">
-        <v>112</v>
+      <c r="U27" s="16" t="str">
+        <v>2338B</v>
       </c>
       <c r="V27" s="13">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="W27" s="13">
-        <v>19.333333333333332</v>
+        <v>2</v>
       </c>
       <c r="X27" s="13">
-        <v>57.666666666666664</v>
+        <v>66</v>
       </c>
       <c r="Y27" s="13">
         <v>0</v>
@@ -10205,22 +13595,22 @@
         <v>5125</v>
       </c>
       <c r="B28" s="12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C28" s="13">
-        <v>1.6666666666666667</v>
+        <v>0.8</v>
       </c>
       <c r="D28" s="13">
-        <v>35.666666666666664</v>
+        <v>37.4</v>
       </c>
       <c r="E28" s="13">
         <v>0</v>
       </c>
       <c r="F28" s="13">
-        <v>37.333333333333336</v>
+        <v>38.200000000000003</v>
       </c>
       <c r="G28" s="12">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H28" s="14">
         <v>1</v>
@@ -10253,22 +13643,22 @@
         <v>0</v>
       </c>
       <c r="R28" s="12">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="T28" s="15">
         <v>24</v>
       </c>
       <c r="U28" s="16">
-        <v>1625</v>
+        <v>111</v>
       </c>
       <c r="V28" s="13">
-        <v>73.333333333333329</v>
+        <v>67.75</v>
       </c>
       <c r="W28" s="13">
-        <v>8.3333333333333339</v>
+        <v>26.75</v>
       </c>
       <c r="X28" s="13">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="Y28" s="13">
         <v>0</v>
@@ -10291,22 +13681,22 @@
         <v>5822</v>
       </c>
       <c r="B29" s="12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C29" s="13">
-        <v>11.333333333333334</v>
+        <v>6.75</v>
       </c>
       <c r="D29" s="13">
-        <v>49</v>
+        <v>28.75</v>
       </c>
       <c r="E29" s="13">
         <v>0</v>
       </c>
       <c r="F29" s="13">
-        <v>60.333333333333336</v>
+        <v>35.5</v>
       </c>
       <c r="G29" s="12">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="H29" s="14">
         <v>1</v>
@@ -10339,22 +13729,22 @@
         <v>0</v>
       </c>
       <c r="R29" s="12">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="T29" s="15">
         <v>25</v>
       </c>
-      <c r="U29" s="16" t="str">
-        <v>2338B</v>
+      <c r="U29" s="16">
+        <v>3197</v>
       </c>
       <c r="V29" s="13">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="W29" s="13">
-        <v>4.666666666666667</v>
+        <v>9.25</v>
       </c>
       <c r="X29" s="13">
-        <v>58.333333333333336</v>
+        <v>57.75</v>
       </c>
       <c r="Y29" s="13">
         <v>0</v>
@@ -10380,19 +13770,19 @@
         <v>3</v>
       </c>
       <c r="C30" s="13">
-        <v>25.666666666666668</v>
+        <v>14.333333333333334</v>
       </c>
       <c r="D30" s="13">
-        <v>102.33333333333333</v>
+        <v>84.333333333333329</v>
       </c>
       <c r="E30" s="13">
         <v>0</v>
       </c>
       <c r="F30" s="13">
-        <v>128</v>
+        <v>98.666666666666671</v>
       </c>
       <c r="G30" s="12">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="H30" s="14">
         <v>1</v>
@@ -10425,7 +13815,7 @@
         <v>0</v>
       </c>
       <c r="R30" s="12">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="T30" s="15">
         <v>26</v>
@@ -10434,13 +13824,13 @@
         <v>4143</v>
       </c>
       <c r="V30" s="13">
-        <v>60.5</v>
+        <v>51.5</v>
       </c>
       <c r="W30" s="13">
-        <v>9.5</v>
+        <v>3</v>
       </c>
       <c r="X30" s="13">
-        <v>51</v>
+        <v>48.5</v>
       </c>
       <c r="Y30" s="13">
         <v>0</v>
@@ -10463,22 +13853,22 @@
         <v>5934</v>
       </c>
       <c r="B31" s="12">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C31" s="13">
-        <v>14.5</v>
+        <v>25.2</v>
       </c>
       <c r="D31" s="13">
-        <v>104</v>
+        <v>50.6</v>
       </c>
       <c r="E31" s="13">
         <v>0</v>
       </c>
       <c r="F31" s="13">
-        <v>118.5</v>
+        <v>75.8</v>
       </c>
       <c r="G31" s="12">
-        <v>129</v>
+        <v>82</v>
       </c>
       <c r="H31" s="14">
         <v>1</v>
@@ -10511,22 +13901,22 @@
         <v>0</v>
       </c>
       <c r="R31" s="12">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="T31" s="15">
         <v>27</v>
       </c>
       <c r="U31" s="16">
-        <v>5822</v>
+        <v>5125</v>
       </c>
       <c r="V31" s="13">
-        <v>60.333333333333336</v>
+        <v>38.200000000000003</v>
       </c>
       <c r="W31" s="13">
-        <v>11.333333333333334</v>
+        <v>0.8</v>
       </c>
       <c r="X31" s="13">
-        <v>49</v>
+        <v>37.4</v>
       </c>
       <c r="Y31" s="13">
         <v>0</v>
@@ -10549,22 +13939,22 @@
         <v>7117</v>
       </c>
       <c r="B32" s="12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C32" s="13">
-        <v>59</v>
+        <v>35.75</v>
       </c>
       <c r="D32" s="13">
-        <v>123</v>
+        <v>69.75</v>
       </c>
       <c r="E32" s="13">
         <v>0</v>
       </c>
       <c r="F32" s="13">
-        <v>182</v>
+        <v>105.5</v>
       </c>
       <c r="G32" s="12">
-        <v>188</v>
+        <v>113</v>
       </c>
       <c r="H32" s="14">
         <v>1</v>
@@ -10597,22 +13987,22 @@
         <v>0</v>
       </c>
       <c r="R32" s="12">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="T32" s="15">
         <v>28</v>
       </c>
       <c r="U32" s="16">
-        <v>648</v>
+        <v>5822</v>
       </c>
       <c r="V32" s="13">
-        <v>59</v>
+        <v>35.5</v>
       </c>
       <c r="W32" s="13">
-        <v>13</v>
+        <v>6.75</v>
       </c>
       <c r="X32" s="13">
-        <v>46</v>
+        <v>28.75</v>
       </c>
       <c r="Y32" s="13">
         <v>0</v>
@@ -10635,22 +14025,22 @@
         <v>7457</v>
       </c>
       <c r="B33" s="12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C33" s="13">
-        <v>50.666666666666664</v>
+        <v>43.2</v>
       </c>
       <c r="D33" s="13">
-        <v>138</v>
+        <v>195.8</v>
       </c>
       <c r="E33" s="13">
         <v>0</v>
       </c>
       <c r="F33" s="13">
-        <v>188.66666666666666</v>
+        <v>239</v>
       </c>
       <c r="G33" s="12">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="H33" s="14">
         <v>1</v>
@@ -10683,22 +14073,22 @@
         <v>0</v>
       </c>
       <c r="R33" s="12">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T33" s="15">
         <v>29</v>
       </c>
-      <c r="U33" s="16">
-        <v>1781</v>
+      <c r="U33" s="16" t="str">
+        <v>1756B</v>
       </c>
       <c r="V33" s="13">
-        <v>48</v>
+        <v>25.333333333333332</v>
       </c>
       <c r="W33" s="13">
-        <v>3.3333333333333335</v>
+        <v>1</v>
       </c>
       <c r="X33" s="13">
-        <v>44.666666666666664</v>
+        <v>24.333333333333332</v>
       </c>
       <c r="Y33" s="13">
         <v>0</v>
@@ -10721,22 +14111,22 @@
         <v>9082</v>
       </c>
       <c r="B34" s="12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C34" s="13">
-        <v>10.333333333333334</v>
+        <v>3.8</v>
       </c>
       <c r="D34" s="13">
-        <v>18</v>
+        <v>19.2</v>
       </c>
       <c r="E34" s="13">
         <v>0</v>
       </c>
       <c r="F34" s="13">
-        <v>28.333333333333332</v>
+        <v>23</v>
       </c>
       <c r="G34" s="12">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H34" s="14">
         <v>1</v>
@@ -10769,22 +14159,22 @@
         <v>0</v>
       </c>
       <c r="R34" s="12">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T34" s="15">
         <v>30</v>
       </c>
       <c r="U34" s="16">
-        <v>1736</v>
+        <v>4423</v>
       </c>
       <c r="V34" s="13">
-        <v>38.333333333333336</v>
+        <v>25.25</v>
       </c>
       <c r="W34" s="13">
-        <v>5.333333333333333</v>
+        <v>2.75</v>
       </c>
       <c r="X34" s="13">
-        <v>33</v>
+        <v>22.5</v>
       </c>
       <c r="Y34" s="13">
         <v>0</v>
@@ -10807,22 +14197,22 @@
         <v>9401</v>
       </c>
       <c r="B35" s="12">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C35" s="13">
-        <v>11.5</v>
+        <v>41.4</v>
       </c>
       <c r="D35" s="13">
-        <v>83.5</v>
+        <v>152.80000000000001</v>
       </c>
       <c r="E35" s="13">
         <v>0</v>
       </c>
       <c r="F35" s="13">
-        <v>95</v>
+        <v>194.2</v>
       </c>
       <c r="G35" s="12">
-        <v>96</v>
+        <v>223</v>
       </c>
       <c r="H35" s="14">
         <v>1</v>
@@ -10855,22 +14245,22 @@
         <v>0</v>
       </c>
       <c r="R35" s="12">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="T35" s="15">
         <v>31</v>
       </c>
       <c r="U35" s="16">
-        <v>5125</v>
+        <v>9082</v>
       </c>
       <c r="V35" s="13">
-        <v>37.333333333333336</v>
+        <v>23</v>
       </c>
       <c r="W35" s="13">
-        <v>1.6666666666666667</v>
+        <v>3.8</v>
       </c>
       <c r="X35" s="13">
-        <v>35.666666666666664</v>
+        <v>19.2</v>
       </c>
       <c r="Y35" s="13">
         <v>0</v>
@@ -10893,22 +14283,22 @@
         <v>11173</v>
       </c>
       <c r="B36" s="12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C36" s="13">
-        <v>10.333333333333334</v>
+        <v>26</v>
       </c>
       <c r="D36" s="13">
-        <v>67.666666666666671</v>
+        <v>51.8</v>
       </c>
       <c r="E36" s="13">
         <v>0</v>
       </c>
       <c r="F36" s="13">
-        <v>78</v>
+        <v>77.8</v>
       </c>
       <c r="G36" s="12">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="H36" s="14">
         <v>1</v>
@@ -10941,22 +14331,22 @@
         <v>0</v>
       </c>
       <c r="R36" s="12">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="T36" s="15">
         <v>32</v>
       </c>
       <c r="U36" s="16">
-        <v>9082</v>
+        <v>2290</v>
       </c>
       <c r="V36" s="13">
-        <v>28.333333333333332</v>
+        <v>21.5</v>
       </c>
       <c r="W36" s="13">
-        <v>10.333333333333334</v>
+        <v>10.25</v>
       </c>
       <c r="X36" s="13">
-        <v>18</v>
+        <v>11.25</v>
       </c>
       <c r="Y36" s="13">
         <v>0</v>
@@ -10979,22 +14369,22 @@
         <v>1706B</v>
       </c>
       <c r="B37" s="12">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C37" s="13">
-        <v>11.5</v>
+        <v>35.4</v>
       </c>
       <c r="D37" s="13">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="E37" s="13">
         <v>0</v>
       </c>
       <c r="F37" s="13">
-        <v>105.5</v>
+        <v>159.4</v>
       </c>
       <c r="G37" s="12">
-        <v>114</v>
+        <v>191</v>
       </c>
       <c r="H37" s="14">
         <v>1</v>
@@ -11027,22 +14417,22 @@
         <v>0</v>
       </c>
       <c r="R37" s="12">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="T37" s="15">
         <v>33</v>
       </c>
       <c r="U37" s="16">
-        <v>4423</v>
+        <v>3397</v>
       </c>
       <c r="V37" s="13">
-        <v>24</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="W37" s="13">
-        <v>5.5</v>
+        <v>0.6</v>
       </c>
       <c r="X37" s="13">
-        <v>18.5</v>
+        <v>18.8</v>
       </c>
       <c r="Y37" s="13">
         <v>0</v>
@@ -11068,19 +14458,19 @@
         <v>3</v>
       </c>
       <c r="C38" s="13">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="D38" s="13">
-        <v>1</v>
+        <v>24.333333333333332</v>
       </c>
       <c r="E38" s="13">
         <v>0</v>
       </c>
       <c r="F38" s="13">
-        <v>1.6666666666666667</v>
+        <v>25.333333333333332</v>
       </c>
       <c r="G38" s="12">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="H38" s="14">
         <v>1</v>
@@ -11113,22 +14503,22 @@
         <v>0</v>
       </c>
       <c r="R38" s="12">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="T38" s="15">
         <v>34</v>
       </c>
       <c r="U38" s="16">
-        <v>3397</v>
+        <v>1781</v>
       </c>
       <c r="V38" s="13">
-        <v>6.666666666666667</v>
+        <v>10.8</v>
       </c>
       <c r="W38" s="13">
-        <v>1</v>
+        <v>7.4</v>
       </c>
       <c r="X38" s="13">
-        <v>5.666666666666667</v>
+        <v>3.4</v>
       </c>
       <c r="Y38" s="13">
         <v>0</v>
@@ -11151,22 +14541,22 @@
         <v>2338B</v>
       </c>
       <c r="B39" s="12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C39" s="13">
-        <v>4.666666666666667</v>
+        <v>2</v>
       </c>
       <c r="D39" s="13">
-        <v>58.333333333333336</v>
+        <v>66</v>
       </c>
       <c r="E39" s="13">
         <v>0</v>
       </c>
       <c r="F39" s="13">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G39" s="12">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H39" s="14">
         <v>1</v>
@@ -11199,22 +14589,22 @@
         <v>0</v>
       </c>
       <c r="R39" s="12">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="T39" s="15">
         <v>35</v>
       </c>
-      <c r="U39" s="16" t="str">
-        <v>1756B</v>
+      <c r="U39" s="16">
+        <v>1736</v>
       </c>
       <c r="V39" s="13">
-        <v>1.6666666666666667</v>
+        <v>1.4</v>
       </c>
       <c r="W39" s="13">
-        <v>0.66666666666666663</v>
+        <v>0.6</v>
       </c>
       <c r="X39" s="13">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="Y39" s="13">
         <v>0</v>
@@ -19260,7 +22650,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{627E78A1-163C-442F-AB67-E2B2854DBA4F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0ABA5BE-D82A-4FBB-ADE6-F84DF372D23B}">
   <dimension ref="A1:AN6"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -19463,7 +22853,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42EFA942-CCAC-4A15-97A5-02FF87918DE5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DD577D3-FC57-461E-A2D1-C2196A374265}">
   <dimension ref="A1:G3000"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -19517,7 +22907,7 @@
       </c>
       <c r="B5" s="15">
         <f>COUNTIF(Scans[Team '#],"&lt;&gt;")</f>
-        <v>96</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13" x14ac:dyDescent="0.3">
@@ -19550,7 +22940,7 @@
       </c>
       <c r="B8" s="15">
         <f>IF(COUNT(INDEX(_xlfn.ANCHORARRAY('TBA Schedule'!$R$5),,1))&gt;0,COUNTIF(INDEX(_xlfn.ANCHORARRAY($A$17),,1),"Not scouted"),"needs schedule")</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C8" t="s">
         <v>98</v>
@@ -19644,101 +23034,200 @@
         <v>91</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="str" cm="1">
-        <f t="array" ref="A17">_xlfn.LET(_xlpm.ty,Scans[Match type],_xlpm.mt,Scans[Match '#],_xlpm.tm,Scans[Team '#],_xlpm.al,Scans[Alliance],_xlpm.sc,Scans[Scout name],_xlpm.rw,ROW(Scans[Team '#]),_xlpm.nT,_xlfn.SEQUENCE(ROWS(_xlpm.tm)),_xlpm.has,_xlpm.tm&lt;&gt;"",_xlpm.qual,_xlpm.has*((_xlpm.ty="Qual")+(_xlpm.ty="")),_xlpm.s,_xlfn.ANCHORARRAY('TBA Schedule'!$R$5),_xlpm.sm,INDEX(_xlpm.s,,1),_xlpm.sa,INDEX(_xlpm.s,,2),_xlpm.st,INDEX(_xlpm.s,,3),_xlpm.nS,_xlfn.SEQUENCE(ROWS(_xlpm.sm)),_xlpm.hasSched,COUNT(_xlpm.sm)&gt;0,_xlpm.dupN,COUNTIFS(Scans[Team '#],_xlpm.tm,Scans[Match '#],_xlpm.mt,Scans[Match type],_xlpm.ty),_xlpm.dup,_xlfn._xlws.FILTER(_xlfn.HSTACK(IF(_xlpm.nT,"Duplicate scan"),_xlpm.mt,_xlpm.tm,_xlpm.al,_xlpm.rw,_xlpm.sc,"Scanned "&amp;_xlpm.dupN&amp;" times: delete the extra row"),_xlpm.has*(_xlpm.dupN&gt;1),""),_xlpm.qm,_xlfn.UNIQUE(_xlfn._xlws.FILTER(_xlpm.mt,_xlpm.qual,"")),_xlpm.nQ,_xlfn.SEQUENCE(ROWS(_xlpm.qm)),_xlpm.qc,COUNTIFS(Scans[Match '#],_xlpm.qm,Scans[Team '#],"&lt;&gt;",Scans[Match type],"Qual")+COUNTIFS(Scans[Match '#],_xlpm.qm,Scans[Team '#],"&lt;&gt;",Scans[Match type],""),_xlpm.cnt,IF(_xlpm.hasSched,"",_xlfn._xlws.FILTER(_xlfn.HSTACK(IF(_xlpm.nQ,"Not 6 scans"),_xlpm.qm,IF(_xlpm.nQ,""),IF(_xlpm.nQ,""),IF(_xlpm.nQ,""),IF(_xlpm.nQ,""),_xlpm.qc&amp;" scans in this match, expected 6"),(_xlpm.qm&lt;&gt;"")*(_xlpm.qc&lt;&gt;6),"")),_xlpm.last,MAX(_xlfn._xlws.FILTER(_xlpm.mt,_xlpm.qual,0)),_xlpm.seen,COUNTIFS(Scans[Match '#],_xlpm.sm,Scans[Team '#],_xlpm.st,Scans[Match type],"Qual")+COUNTIFS(Scans[Match '#],_xlpm.sm,Scans[Team '#],_xlpm.st,Scans[Match type],""),_xlpm.miss,IF(_xlpm.hasSched,_xlfn._xlws.FILTER(_xlfn.HSTACK(IF(_xlpm.nS,"Not scouted"),_xlpm.sm,_xlpm.st,_xlpm.sa,IF(_xlpm.nS,""),IF(_xlpm.nS,""),IF(_xlpm.nS,"Nobody scanned this robot: ask its scout to show the QR code again (Submitted matches)")),ISNUMBER(_xlpm.sm)*(_xlpm.sm&lt;=_xlpm.last)*(_xlpm.seen=0),""),""),_xlpm.inM,COUNTIFS(_xlpm.sm,_xlpm.mt,_xlpm.st,_xlpm.tm),_xlpm.wt,IF(_xlpm.hasSched,_xlfn._xlws.FILTER(_xlfn.HSTACK(IF(_xlpm.nT,"Team not in that match"),_xlpm.mt,_xlpm.tm,_xlpm.al,_xlpm.rw,_xlpm.sc,IF(COUNTIFS(_xlpm.sm,_xlpm.mt)&gt;0,"Typo in Team #? Check the schedule for this match","There is no such qual match on the TBA schedule")),_xlpm.qual*(_xlpm.inM=0),""),""),_xlpm.inA,COUNTIFS(_xlpm.sm,_xlpm.mt,_xlpm.st,_xlpm.tm,_xlpm.sa,_xlpm.al),_xlpm.wa,IF(_xlpm.hasSched,_xlfn._xlws.FILTER(_xlfn.HSTACK(IF(_xlpm.nT,"Wrong alliance"),_xlpm.mt,_xlpm.tm,_xlpm.al,_xlpm.rw,_xlpm.sc,"The schedule says "&amp;_xlfn.XLOOKUP(_xlpm.mt&amp;"|"&amp;_xlpm.tm,_xlpm.sm&amp;"|"&amp;_xlpm.st,_xlpm.sa,"?")),_xlpm.qual*(_xlpm.inM&gt;0)*(_xlpm.inA=0),""),""),_xlpm.tl,_xlfn.ANCHORARRAY('TBA Teams'!$R$5),_xlpm.tn,INDEX(_xlpm.tl,,1),_xlpm.hasTeams,COUNT(_xlpm.tn)&gt;0,_xlpm.ne,IF(_xlpm.hasTeams*NOT(_xlpm.hasSched),_xlfn._xlws.FILTER(_xlfn.HSTACK(IF(_xlpm.nT,"Team not at this event"),_xlpm.mt,_xlpm.tm,_xlpm.al,_xlpm.rw,_xlpm.sc,IF(_xlpm.nT,"Not on TBA's team list for this event: typo in Team #?")),_xlpm.has*(COUNTIFS(_xlpm.tn,_xlpm.tm)=0),""),""),_xlpm.all,_xlfn.VSTACK(_xlpm.dup,_xlpm.cnt,_xlpm.miss,_xlpm.wt,_xlpm.ne,_xlpm.wa),_xlfn._xlws.FILTER(_xlpm.all,IFERROR(INDEX(_xlpm.all,,1)&lt;&gt;"",FALSE),"✓ Nothing to fix"))</f>
-        <v>✓ Nothing to fix</v>
-      </c>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="array" ref="A17:G22">_xlfn.LET(_xlpm.ty,Scans[Match type],_xlpm.mt,Scans[Match '#],_xlpm.tm,Scans[Team '#],_xlpm.al,Scans[Alliance],_xlpm.sc,Scans[Scout name],_xlpm.rw,ROW(Scans[Team '#]),_xlpm.nT,_xlfn.SEQUENCE(ROWS(_xlpm.tm)),_xlpm.has,_xlpm.tm&lt;&gt;"",_xlpm.qual,_xlpm.has*((_xlpm.ty="Qual")+(_xlpm.ty="")),_xlpm.s,_xlfn.ANCHORARRAY('TBA Schedule'!$R$5),_xlpm.sm,INDEX(_xlpm.s,,1),_xlpm.sa,INDEX(_xlpm.s,,2),_xlpm.st,INDEX(_xlpm.s,,3),_xlpm.nS,_xlfn.SEQUENCE(ROWS(_xlpm.sm)),_xlpm.hasSched,COUNT(_xlpm.sm)&gt;0,_xlpm.dupN,COUNTIFS(Scans[Team '#],_xlpm.tm,Scans[Match '#],_xlpm.mt,Scans[Match type],_xlpm.ty),_xlpm.dup,_xlfn._xlws.FILTER(_xlfn.HSTACK(IF(_xlpm.nT,"Duplicate scan"),_xlpm.mt,_xlpm.tm,_xlpm.al,_xlpm.rw,_xlpm.sc,"Scanned "&amp;_xlpm.dupN&amp;" times: delete the extra row"),_xlpm.has*(_xlpm.dupN&gt;1),""),_xlpm.qm,_xlfn.UNIQUE(_xlfn._xlws.FILTER(_xlpm.mt,_xlpm.qual,"")),_xlpm.nQ,_xlfn.SEQUENCE(ROWS(_xlpm.qm)),_xlpm.qc,COUNTIFS(Scans[Match '#],_xlpm.qm,Scans[Team '#],"&lt;&gt;",Scans[Match type],"Qual")+COUNTIFS(Scans[Match '#],_xlpm.qm,Scans[Team '#],"&lt;&gt;",Scans[Match type],""),_xlpm.cnt,IF(_xlpm.hasSched,"",_xlfn._xlws.FILTER(_xlfn.HSTACK(IF(_xlpm.nQ,"Not 6 scans"),_xlpm.qm,IF(_xlpm.nQ,""),IF(_xlpm.nQ,""),IF(_xlpm.nQ,""),IF(_xlpm.nQ,""),_xlpm.qc&amp;" scans in this match, expected 6"),(_xlpm.qm&lt;&gt;"")*(_xlpm.qc&lt;&gt;6),"")),_xlpm.last,MAX(_xlfn._xlws.FILTER(_xlpm.mt,_xlpm.qual,0)),_xlpm.seen,COUNTIFS(Scans[Match '#],_xlpm.sm,Scans[Team '#],_xlpm.st,Scans[Match type],"Qual")+COUNTIFS(Scans[Match '#],_xlpm.sm,Scans[Team '#],_xlpm.st,Scans[Match type],""),_xlpm.miss,IF(_xlpm.hasSched,_xlfn._xlws.FILTER(_xlfn.HSTACK(IF(_xlpm.nS,"Not scouted"),_xlpm.sm,_xlpm.st,_xlpm.sa,IF(_xlpm.nS,""),IF(_xlpm.nS,""),IF(_xlpm.nS,"Nobody scanned this robot: ask its scout to show the QR code again (Submitted matches)")),ISNUMBER(_xlpm.sm)*(_xlpm.sm&lt;=_xlpm.last)*(_xlpm.seen=0),""),""),_xlpm.inM,COUNTIFS(_xlpm.sm,_xlpm.mt,_xlpm.st,_xlpm.tm),_xlpm.wt,IF(_xlpm.hasSched,_xlfn._xlws.FILTER(_xlfn.HSTACK(IF(_xlpm.nT,"Team not in that match"),_xlpm.mt,_xlpm.tm,_xlpm.al,_xlpm.rw,_xlpm.sc,IF(COUNTIFS(_xlpm.sm,_xlpm.mt)&gt;0,"Typo in Team #? Check the schedule for this match","There is no such qual match on the TBA schedule")),_xlpm.qual*(_xlpm.inM=0),""),""),_xlpm.inA,COUNTIFS(_xlpm.sm,_xlpm.mt,_xlpm.st,_xlpm.tm,_xlpm.sa,_xlpm.al),_xlpm.wa,IF(_xlpm.hasSched,_xlfn._xlws.FILTER(_xlfn.HSTACK(IF(_xlpm.nT,"Wrong alliance"),_xlpm.mt,_xlpm.tm,_xlpm.al,_xlpm.rw,_xlpm.sc,"The schedule says "&amp;_xlfn.XLOOKUP(_xlpm.mt&amp;"|"&amp;_xlpm.tm,_xlpm.sm&amp;"|"&amp;_xlpm.st,_xlpm.sa,"?")),_xlpm.qual*(_xlpm.inM&gt;0)*(_xlpm.inA=0),""),""),_xlpm.tl,_xlfn.ANCHORARRAY('TBA Teams'!$R$5),_xlpm.tn,INDEX(_xlpm.tl,,1),_xlpm.hasTeams,COUNT(_xlpm.tn)&gt;0,_xlpm.ne,IF(_xlpm.hasTeams*NOT(_xlpm.hasSched),_xlfn._xlws.FILTER(_xlfn.HSTACK(IF(_xlpm.nT,"Team not at this event"),_xlpm.mt,_xlpm.tm,_xlpm.al,_xlpm.rw,_xlpm.sc,IF(_xlpm.nT,"Not on TBA's team list for this event: typo in Team #?")),_xlpm.has*(COUNTIFS(_xlpm.tn,_xlpm.tm)=0),""),""),_xlpm.all,_xlfn.VSTACK(_xlpm.dup,_xlpm.cnt,_xlpm.miss,_xlpm.wt,_xlpm.ne,_xlpm.wa),_xlfn._xlws.FILTER(_xlpm.all,IFERROR(INDEX(_xlpm.all,,1)&lt;&gt;"",FALSE),"✓ Nothing to fix"))</f>
+        <v>Not scouted</v>
+      </c>
+      <c r="B17" s="15">
+        <v>19</v>
+      </c>
+      <c r="C17" s="15">
+        <v>1706</v>
+      </c>
+      <c r="D17" s="15" t="str">
+        <v>Red</v>
+      </c>
+      <c r="E17" s="15" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v>Nobody scanned this robot: ask its scout to show the QR code again (Submitted matches)</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="str">
+        <v>Not scouted</v>
+      </c>
+      <c r="B18" s="15">
+        <v>19</v>
+      </c>
+      <c r="C18" s="15">
+        <v>4256</v>
+      </c>
+      <c r="D18" s="15" t="str">
+        <v>Red</v>
+      </c>
+      <c r="E18" s="15" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v>Nobody scanned this robot: ask its scout to show the QR code again (Submitted matches)</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="str">
+        <v>Not scouted</v>
+      </c>
+      <c r="B19" s="15">
+        <v>19</v>
+      </c>
+      <c r="C19" s="15" t="str">
+        <v>2338B</v>
+      </c>
+      <c r="D19" s="15" t="str">
+        <v>Red</v>
+      </c>
+      <c r="E19" s="15" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v>Nobody scanned this robot: ask its scout to show the QR code again (Submitted matches)</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="str">
+        <v>Not scouted</v>
+      </c>
+      <c r="B20" s="15">
+        <v>19</v>
+      </c>
+      <c r="C20" s="15">
+        <v>5847</v>
+      </c>
+      <c r="D20" s="15" t="str">
+        <v>Blue</v>
+      </c>
+      <c r="E20" s="15" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v>Nobody scanned this robot: ask its scout to show the QR code again (Submitted matches)</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="str">
+        <v>Not scouted</v>
+      </c>
+      <c r="B21" s="15">
+        <v>19</v>
+      </c>
+      <c r="C21" s="15">
+        <v>1306</v>
+      </c>
+      <c r="D21" s="15" t="str">
+        <v>Blue</v>
+      </c>
+      <c r="E21" s="15" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v>Nobody scanned this robot: ask its scout to show the QR code again (Submitted matches)</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" t="str">
+        <v>Not scouted</v>
+      </c>
+      <c r="B22" s="15">
+        <v>19</v>
+      </c>
+      <c r="C22" s="15" t="str">
+        <v>1756B</v>
+      </c>
+      <c r="D22" s="15" t="str">
+        <v>Blue</v>
+      </c>
+      <c r="E22" s="15" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v>Nobody scanned this robot: ask its scout to show the QR code again (Submitted matches)</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
       <c r="D23" s="15"/>
       <c r="E23" s="15"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B24" s="15"/>
       <c r="C24" s="15"/>
       <c r="D24" s="15"/>
       <c r="E24" s="15"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
       <c r="D25" s="15"/>
       <c r="E25" s="15"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B26" s="15"/>
       <c r="C26" s="15"/>
       <c r="D26" s="15"/>
       <c r="E26" s="15"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B27" s="15"/>
       <c r="C27" s="15"/>
       <c r="D27" s="15"/>
       <c r="E27" s="15"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B28" s="15"/>
       <c r="C28" s="15"/>
       <c r="D28" s="15"/>
       <c r="E28" s="15"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B29" s="15"/>
       <c r="C29" s="15"/>
       <c r="D29" s="15"/>
       <c r="E29" s="15"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B30" s="15"/>
       <c r="C30" s="15"/>
       <c r="D30" s="15"/>
       <c r="E30" s="15"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
       <c r="D31" s="15"/>
       <c r="E31" s="15"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B32" s="15"/>
       <c r="C32" s="15"/>
       <c r="D32" s="15"/>
@@ -37567,7 +41056,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9395D35-90D1-4292-AEF6-9750A7CFA102}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73EFC9E5-FDC8-453A-9FD5-0F448B251C07}">
   <dimension ref="A1:T185"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -40196,7 +43685,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93DD3CAB-6492-4F81-9093-74F80CAAFC05}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06ADC7D3-88FB-46AD-91BD-E28A803C4BD0}">
   <dimension ref="A1:S40"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
